--- a/output/spreadsheet/apartment_research_march18_2026.xlsx
+++ b/output/spreadsheet/apartment_research_march18_2026.xlsx
@@ -451,7 +451,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AD19"/>
+  <dimension ref="A1:AD26"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="34" customWidth="1" min="1" max="1"/>
@@ -634,12 +634,12 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Stanford Villa</t>
+          <t>Landsby</t>
         </is>
       </c>
       <c r="B2" s="2" t="inlineStr">
         <is>
-          <t>Palo Alto</t>
+          <t>Mountain View</t>
         </is>
       </c>
       <c r="C2" s="2" t="inlineStr">
@@ -669,64 +669,60 @@
       </c>
       <c r="H2" s="2" t="inlineStr">
         <is>
-          <t>1,000-1,050</t>
+          <t>964-1,047</t>
         </is>
       </c>
       <c r="I2" s="2" t="inlineStr">
         <is>
-          <t>$3,650-$4,170</t>
+          <t>$5,618-$5,710</t>
         </is>
       </c>
       <c r="J2" s="2" t="inlineStr">
         <is>
-          <t>Base rent</t>
+          <t>Total monthly price</t>
         </is>
       </c>
       <c r="K2" s="2" t="inlineStr">
         <is>
-          <t>Sequoia (Units 106 now, 140 Apr 1); Ponderosa (multiple units now)</t>
-        </is>
-      </c>
-      <c r="L2" s="2" t="inlineStr"/>
-      <c r="M2" s="2" t="inlineStr">
-        <is>
-          <t>$800</t>
-        </is>
-      </c>
-      <c r="N2" s="2" t="inlineStr"/>
+          <t>2A-6 / Unit 1511 now; 2K-1 / Unit 3521 Mar 21; 2B-1 / Unit 3319 Mar 23</t>
+        </is>
+      </c>
+      <c r="L2" s="2" t="n"/>
+      <c r="M2" s="2" t="n"/>
+      <c r="N2" s="2" t="n"/>
       <c r="O2" s="2" t="inlineStr">
         <is>
-          <t>3.9 (5 reviews)</t>
+          <t>4.6 (57 reviews)</t>
         </is>
       </c>
       <c r="P2" s="3" t="inlineStr">
         <is>
-          <t>https://www.stanfordvilla.com/apartments/ca/palo-alto/amenities</t>
+          <t>https://livelandsby.com/</t>
         </is>
       </c>
       <c r="Q2" s="3" t="inlineStr">
         <is>
-          <t>https://www.apartments.com/stanford-villa-palo-alto-ca/5ezwzbq/</t>
+          <t>https://www.apartments.com/landsby-mountain-view-ca/8mzlqg0/</t>
         </is>
       </c>
       <c r="R2" s="2" t="inlineStr">
         <is>
-          <t>California Ave</t>
+          <t>San Antonio</t>
         </is>
       </c>
       <c r="S2" s="2" t="inlineStr">
         <is>
-          <t>1.5 mi</t>
+          <t>0.2 mi</t>
         </is>
       </c>
       <c r="T2" s="2" t="inlineStr">
         <is>
-          <t>30 min</t>
+          <t>4 min</t>
         </is>
       </c>
       <c r="U2" s="2" t="inlineStr">
         <is>
-          <t>Two 2B/2B floorplans were live: Sequoia 1,000 sq ft and Ponderosa 1,050 sq ft.</t>
+          <t>A second 2B-1 unit for May 8 was excluded from the eligible interpretation.</t>
         </is>
       </c>
       <c r="V2" s="2" t="inlineStr">
@@ -741,29 +737,29 @@
       </c>
       <c r="X2" t="inlineStr">
         <is>
-          <t>Estimated from walking distance at 20 min/mile</t>
+          <t>Listing-provided walking time</t>
         </is>
       </c>
       <c r="Y2" t="inlineStr">
         <is>
-          <t>No in-unit washer/dryer</t>
+          <t>In-unit washer/dryer</t>
         </is>
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>No in-unit laundry; official site lists on-site laundry facilities (card-operated), and Apartments.com says on-site laundry is shared resident use.</t>
+          <t>Apartments.com says Landsby has in-unit washers/dryers; official amenities page lists a GE front-load washer &amp; dryer in select homes.</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
         <is>
-          <t>Official sources confirm on-site shared laundry rather than in-unit laundry. California Ave is the closest Caltrain stop; LoopNet showed 1.5 mi and Apartments.com showed 1.8 mi, so 1.5 mi was used.</t>
+          <t>Official site says Landsby is a short walk to San Antonio Caltrain; Apartments.com lists San Antonio at 0.2 mi / 4 min walk and confirms in-unit laundry.</t>
         </is>
       </c>
       <c r="AB2" t="inlineStr">
         <is>
-          <t>https://rde.stanford.edu/studenthousing/stanford-villa-apartments
-https://www.apartments.com/stanford-villa-palo-alto-ca/5ezwzbq/
-https://www.loopnet.com/property/3375-alma-st-palo-alto-ca-94306/06085-13228075/</t>
+          <t>https://livelandsby.com/
+https://livelandsby.com/amenities/
+https://www.apartments.com/landsby-mountain-view-ca/8mzlqg0/</t>
         </is>
       </c>
       <c r="AC2" t="inlineStr">
@@ -772,146 +768,1600 @@
         </is>
       </c>
       <c r="AD2" t="n">
-        <v>0.89</v>
+        <v>0.97</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
+          <t>MV Apartments</t>
+        </is>
+      </c>
+      <c r="B3" s="2" t="inlineStr">
+        <is>
+          <t>Mountain View</t>
+        </is>
+      </c>
+      <c r="C3" s="2" t="inlineStr">
+        <is>
+          <t>ELIGIBLE</t>
+        </is>
+      </c>
+      <c r="D3" s="2" t="inlineStr">
+        <is>
+          <t>Now</t>
+        </is>
+      </c>
+      <c r="E3" s="2" t="inlineStr">
+        <is>
+          <t>2026-04-10</t>
+        </is>
+      </c>
+      <c r="F3" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="G3" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="H3" s="2" t="inlineStr">
+        <is>
+          <t>1,013</t>
+        </is>
+      </c>
+      <c r="I3" s="2" t="inlineStr">
+        <is>
+          <t>$5,549</t>
+        </is>
+      </c>
+      <c r="J3" s="2" t="inlineStr">
+        <is>
+          <t>Base rent</t>
+        </is>
+      </c>
+      <c r="K3" s="2" t="inlineStr">
+        <is>
+          <t>Chestnut / Unit 528 now</t>
+        </is>
+      </c>
+      <c r="L3" s="2" t="n"/>
+      <c r="M3" s="2" t="n"/>
+      <c r="N3" s="2" t="n"/>
+      <c r="O3" s="2" t="inlineStr">
+        <is>
+          <t>4.8 (13 reviews)</t>
+        </is>
+      </c>
+      <c r="P3" s="3" t="inlineStr">
+        <is>
+          <t>https://www.mvapartments.com/</t>
+        </is>
+      </c>
+      <c r="Q3" s="3" t="inlineStr">
+        <is>
+          <t>https://www.apartments.com/mv-apartments-mountain-view-ca/tlm9sdb/</t>
+        </is>
+      </c>
+      <c r="R3" s="2" t="inlineStr">
+        <is>
+          <t>San Antonio</t>
+        </is>
+      </c>
+      <c r="S3" s="2" t="inlineStr">
+        <is>
+          <t>0.9 mi</t>
+        </is>
+      </c>
+      <c r="T3" s="2" t="inlineStr">
+        <is>
+          <t>16 min</t>
+        </is>
+      </c>
+      <c r="U3" s="2" t="inlineStr">
+        <is>
+          <t>A second Chestnut unit for Apr 14 was excluded from the eligible interpretation because it is after the cutoff.</t>
+        </is>
+      </c>
+      <c r="V3" s="2" t="inlineStr">
+        <is>
+          <t>2026-03-17</t>
+        </is>
+      </c>
+      <c r="W3" s="2" t="inlineStr">
+        <is>
+          <t>Apartments.com live floor plan page</t>
+        </is>
+      </c>
+      <c r="X3" t="inlineStr">
+        <is>
+          <t>Listing-stated walking time on Apartments.com</t>
+        </is>
+      </c>
+      <c r="Y3" t="inlineStr">
+        <is>
+          <t>In-unit washer/dryer</t>
+        </is>
+      </c>
+      <c r="Z3" t="inlineStr">
+        <is>
+          <t>Official site lists in-home laundry appliances and a full-size front-loading washer and dryer; Apartments.com also lists in-unit washers and dryers.</t>
+        </is>
+      </c>
+      <c r="AA3" t="inlineStr">
+        <is>
+          <t>Official MV Apartments site advertises in-home laundry appliances/full-size front-loading washer and dryer. Apartments.com lists San Antonio at 0.9 mi / 16 min walk.</t>
+        </is>
+      </c>
+      <c r="AB3" t="inlineStr">
+        <is>
+          <t>https://www.mvapartments.com/
+https://www.apartments.com/mv-apartments-mountain-view-ca/tlm9sdb/</t>
+        </is>
+      </c>
+      <c r="AC3" t="inlineStr">
+        <is>
+          <t>2026-03-18</t>
+        </is>
+      </c>
+      <c r="AD3" t="n">
+        <v>0.96</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="2" t="inlineStr">
+        <is>
+          <t>Maplewood Apartments</t>
+        </is>
+      </c>
+      <c r="B4" s="2" t="inlineStr">
+        <is>
+          <t>Mountain View</t>
+        </is>
+      </c>
+      <c r="C4" s="2" t="inlineStr">
+        <is>
+          <t>ELIGIBLE</t>
+        </is>
+      </c>
+      <c r="D4" s="2" t="inlineStr">
+        <is>
+          <t>Now</t>
+        </is>
+      </c>
+      <c r="E4" s="2" t="inlineStr">
+        <is>
+          <t>2026-04-10</t>
+        </is>
+      </c>
+      <c r="F4" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="G4" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="H4" s="2" t="inlineStr">
+        <is>
+          <t>947</t>
+        </is>
+      </c>
+      <c r="I4" s="2" t="inlineStr">
+        <is>
+          <t>$3,700-$3,800</t>
+        </is>
+      </c>
+      <c r="J4" s="2" t="inlineStr">
+        <is>
+          <t>Base rent</t>
+        </is>
+      </c>
+      <c r="K4" s="2" t="inlineStr">
+        <is>
+          <t>Plan B1 / Unit 29 now; Unit 31 Apr 7</t>
+        </is>
+      </c>
+      <c r="L4" s="2" t="inlineStr">
+        <is>
+          <t>Up to 1 month on us</t>
+        </is>
+      </c>
+      <c r="M4" s="2" t="inlineStr">
+        <is>
+          <t>$600</t>
+        </is>
+      </c>
+      <c r="N4" s="2" t="n"/>
+      <c r="O4" s="2" t="inlineStr">
+        <is>
+          <t>4.0 (0 reviews)</t>
+        </is>
+      </c>
+      <c r="P4" s="3" t="inlineStr">
+        <is>
+          <t>https://livemaplewoodca.com/amenities.aspx</t>
+        </is>
+      </c>
+      <c r="Q4" s="3" t="inlineStr">
+        <is>
+          <t>https://www.apartments.com/maplewood-apartments-mountain-view-ca/0h511d1/</t>
+        </is>
+      </c>
+      <c r="R4" s="2" t="inlineStr">
+        <is>
+          <t>Mountain View</t>
+        </is>
+      </c>
+      <c r="S4" s="2" t="inlineStr">
+        <is>
+          <t>1.3 mi</t>
+        </is>
+      </c>
+      <c r="T4" s="2" t="inlineStr">
+        <is>
+          <t>26 min</t>
+        </is>
+      </c>
+      <c r="U4" s="2" t="inlineStr">
+        <is>
+          <t>Two 2B/2B units were live and both meet the early-April cutoff.</t>
+        </is>
+      </c>
+      <c r="V4" s="2" t="inlineStr">
+        <is>
+          <t>2026-03-17</t>
+        </is>
+      </c>
+      <c r="W4" s="2" t="inlineStr">
+        <is>
+          <t>Apartments.com live floor plan page</t>
+        </is>
+      </c>
+      <c r="X4" t="inlineStr">
+        <is>
+          <t>Estimated from the listed 1.3 mi distance at 20 min/mile; no published walking route was found</t>
+        </is>
+      </c>
+      <c r="Y4" t="inlineStr">
+        <is>
+          <t>In-unit washer/dryer</t>
+        </is>
+      </c>
+      <c r="Z4" t="inlineStr">
+        <is>
+          <t>Official site lists In-Home Washer &amp; Dryer; Apartments.com also says units have in-unit washers and dryers.</t>
+        </is>
+      </c>
+      <c r="AA4" t="inlineStr">
+        <is>
+          <t>Official Maplewood site shows 1885 California St and in-home washer/dryer. Apartments.com lists Mountain View Caltrain at 1.3 mi and San Antonio at 1.5 mi.</t>
+        </is>
+      </c>
+      <c r="AB4" t="inlineStr">
+        <is>
+          <t>https://livemaplewoodca.com/amenities.aspx
+https://www.apartments.com/maplewood-apartments-mountain-view-ca/0h511d1/
+https://www.apartmentfinder.com/California/Mountain-View-Apartments/Maplewood-Apartments</t>
+        </is>
+      </c>
+      <c r="AC4" t="inlineStr">
+        <is>
+          <t>2026-03-18</t>
+        </is>
+      </c>
+      <c r="AD4" t="n">
+        <v>0.68</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="2" t="inlineStr">
+        <is>
+          <t>Montrose</t>
+        </is>
+      </c>
+      <c r="B5" s="2" t="inlineStr">
+        <is>
+          <t>Mountain View</t>
+        </is>
+      </c>
+      <c r="C5" s="2" t="inlineStr">
+        <is>
+          <t>ELIGIBLE</t>
+        </is>
+      </c>
+      <c r="D5" s="2" t="inlineStr">
+        <is>
+          <t>Now</t>
+        </is>
+      </c>
+      <c r="E5" s="2" t="inlineStr">
+        <is>
+          <t>2026-04-10</t>
+        </is>
+      </c>
+      <c r="F5" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="G5" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="H5" s="2" t="inlineStr">
+        <is>
+          <t>1,094-1,289</t>
+        </is>
+      </c>
+      <c r="I5" s="2" t="inlineStr">
+        <is>
+          <t>$5,108-$5,605</t>
+        </is>
+      </c>
+      <c r="J5" s="2" t="inlineStr">
+        <is>
+          <t>Base rent</t>
+        </is>
+      </c>
+      <c r="K5" s="2" t="inlineStr">
+        <is>
+          <t>2C (Units 303, 256 now; Unit 1211 Apr 5)</t>
+        </is>
+      </c>
+      <c r="L5" s="2" t="n"/>
+      <c r="M5" s="2" t="n"/>
+      <c r="N5" s="2" t="inlineStr">
+        <is>
+          <t>Month-to-month and short-term leases available</t>
+        </is>
+      </c>
+      <c r="O5" s="2" t="inlineStr">
+        <is>
+          <t>5.0 (0 reviews)</t>
+        </is>
+      </c>
+      <c r="P5" s="3" t="inlineStr">
+        <is>
+          <t>https://prometheusapartments.com/ca/mountain-view-apartments/montrose</t>
+        </is>
+      </c>
+      <c r="Q5" s="3" t="inlineStr">
+        <is>
+          <t>https://www.apartments.com/montrose-mountain-view-ca/8875n40/</t>
+        </is>
+      </c>
+      <c r="R5" s="2" t="inlineStr">
+        <is>
+          <t>Mountain View</t>
+        </is>
+      </c>
+      <c r="S5" s="2" t="inlineStr">
+        <is>
+          <t>1.8 mi</t>
+        </is>
+      </c>
+      <c r="T5" s="2" t="inlineStr">
+        <is>
+          <t>36 min</t>
+        </is>
+      </c>
+      <c r="U5" s="2" t="inlineStr">
+        <is>
+          <t>Live 2B/2B units are posted now and on Apr 5, but the property is materially farther from Caltrain on foot than Dean, Verve, or MV Apartments.</t>
+        </is>
+      </c>
+      <c r="V5" s="2" t="inlineStr">
+        <is>
+          <t>2026-03-18</t>
+        </is>
+      </c>
+      <c r="W5" s="2" t="inlineStr">
+        <is>
+          <t>Apartments.com exact property page plus ApartmentHomeLiving 2-bedroom availability</t>
+        </is>
+      </c>
+      <c r="X5" t="inlineStr">
+        <is>
+          <t>Estimated from routed walking distance to Mountain View Caltrain using a map routing tool at 20 min/mile because the listing only exposed drive distance to Caltrain</t>
+        </is>
+      </c>
+      <c r="Y5" t="inlineStr">
+        <is>
+          <t>In-unit washer/dryer</t>
+        </is>
+      </c>
+      <c r="Z5" t="inlineStr">
+        <is>
+          <t>Apartments.com lists Washer/Dryer in apartment features for Montrose.</t>
+        </is>
+      </c>
+      <c r="AA5" t="inlineStr">
+        <is>
+          <t>Apartments.com confirms in-unit washer/dryer. Because the page only exposed drive-distance Caltrain info, the walk metric was estimated from a routed walking path to Mountain View Caltrain.</t>
+        </is>
+      </c>
+      <c r="AB5" t="inlineStr">
+        <is>
+          <t>https://prometheusapartments.com/ca/mountain-view-apartments/montrose
+https://www.apartments.com/montrose-mountain-view-ca/8875n40/
+https://www.apartmenthomeliving.com/mountain-view-ca/san-antonio/apartments-for-rent/2-bedroom</t>
+        </is>
+      </c>
+      <c r="AC5" t="inlineStr">
+        <is>
+          <t>2026-03-18</t>
+        </is>
+      </c>
+      <c r="AD5" t="n">
+        <v>0.83</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="2" t="inlineStr">
+        <is>
+          <t>Rowe at Pear Village</t>
+        </is>
+      </c>
+      <c r="B6" s="2" t="inlineStr">
+        <is>
+          <t>Mountain View</t>
+        </is>
+      </c>
+      <c r="C6" s="2" t="inlineStr">
+        <is>
+          <t>ELIGIBLE</t>
+        </is>
+      </c>
+      <c r="D6" s="2" t="inlineStr">
+        <is>
+          <t>2026-03-22</t>
+        </is>
+      </c>
+      <c r="E6" s="2" t="inlineStr">
+        <is>
+          <t>2026-04-10</t>
+        </is>
+      </c>
+      <c r="F6" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="G6" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="H6" s="2" t="inlineStr">
+        <is>
+          <t>1,146-1,318</t>
+        </is>
+      </c>
+      <c r="I6" s="2" t="inlineStr">
+        <is>
+          <t>$5,190-$5,650</t>
+        </is>
+      </c>
+      <c r="J6" s="2" t="inlineStr">
+        <is>
+          <t>Total monthly price</t>
+        </is>
+      </c>
+      <c r="K6" s="2" t="inlineStr">
+        <is>
+          <t>Unit 260 (1,146 sq ft, Mar 22); 2A.2 / Unit 332 (1,318 sq ft, Mar 25)</t>
+        </is>
+      </c>
+      <c r="L6" s="2" t="n"/>
+      <c r="M6" s="2" t="n"/>
+      <c r="N6" s="2" t="n"/>
+      <c r="O6" s="2" t="inlineStr">
+        <is>
+          <t>4.9 (11 reviews)</t>
+        </is>
+      </c>
+      <c r="P6" s="3" t="inlineStr">
+        <is>
+          <t>https://rowepearvillage.com/amenities/</t>
+        </is>
+      </c>
+      <c r="Q6" s="3" t="inlineStr">
+        <is>
+          <t>https://www.apartments.com/rowe-at-pear-village-mountain-view-ca/7fyfd6x/</t>
+        </is>
+      </c>
+      <c r="R6" s="2" t="inlineStr">
+        <is>
+          <t>Mountain View</t>
+        </is>
+      </c>
+      <c r="S6" s="2" t="inlineStr">
+        <is>
+          <t>1.13 mi</t>
+        </is>
+      </c>
+      <c r="T6" s="2" t="inlineStr">
+        <is>
+          <t>23 min</t>
+        </is>
+      </c>
+      <c r="U6" s="2" t="inlineStr">
+        <is>
+          <t>A May 7 unit was excluded from the eligible interpretation because it misses the early-April cutoff.</t>
+        </is>
+      </c>
+      <c r="V6" s="2" t="inlineStr">
+        <is>
+          <t>2026-03-17</t>
+        </is>
+      </c>
+      <c r="W6" s="2" t="inlineStr">
+        <is>
+          <t>Apartments.com live floor plan page</t>
+        </is>
+      </c>
+      <c r="X6" t="inlineStr">
+        <is>
+          <t>Estimated from the listed 1.13 mi distance at 20 min/mile</t>
+        </is>
+      </c>
+      <c r="Y6" t="inlineStr">
+        <is>
+          <t>In-unit washer/dryer</t>
+        </is>
+      </c>
+      <c r="Z6" t="inlineStr">
+        <is>
+          <t>Official site says Whirlpool front-load washer and dryer in unit; Apartments.com and Zillow also list in-unit laundry.</t>
+        </is>
+      </c>
+      <c r="AA6" t="inlineStr">
+        <is>
+          <t>Official amenities page lists in-unit washer/dryer. ApartmentHomeLiving lists Mountain View Caltrain at 1.13 mi; no direct walking route was exposed, so time was estimated.</t>
+        </is>
+      </c>
+      <c r="AB6" t="inlineStr">
+        <is>
+          <t>https://rowepearvillage.com/amenities/
+https://www.apartments.com/rowe-at-pear-village-mountain-view-ca/7fyfd6x/
+https://www.apartmenthomeliving.com/apartment-finder/Rowe-at-Pear-Village-Mountain-View-CA-94043-19859551
+https://www.caltrain.com/station/mountainview</t>
+        </is>
+      </c>
+      <c r="AC6" t="inlineStr">
+        <is>
+          <t>2026-03-18</t>
+        </is>
+      </c>
+      <c r="AD6" t="n">
+        <v>0.79</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="2" t="inlineStr">
+        <is>
+          <t>Sevens</t>
+        </is>
+      </c>
+      <c r="B7" s="2" t="inlineStr">
+        <is>
+          <t>Mountain View</t>
+        </is>
+      </c>
+      <c r="C7" s="2" t="inlineStr">
+        <is>
+          <t>ELIGIBLE</t>
+        </is>
+      </c>
+      <c r="D7" s="2" t="inlineStr">
+        <is>
+          <t>Now</t>
+        </is>
+      </c>
+      <c r="E7" s="2" t="inlineStr">
+        <is>
+          <t>2026-04-10</t>
+        </is>
+      </c>
+      <c r="F7" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="G7" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="H7" s="2" t="inlineStr">
+        <is>
+          <t>1,021-1,240+</t>
+        </is>
+      </c>
+      <c r="I7" s="2" t="inlineStr">
+        <is>
+          <t>$5,979-$7,184</t>
+        </is>
+      </c>
+      <c r="J7" s="2" t="inlineStr">
+        <is>
+          <t>Total monthly price</t>
+        </is>
+      </c>
+      <c r="K7" s="2" t="inlineStr">
+        <is>
+          <t>B4 (Units B-130 now, B-276 now, B-176 Mar 31, B-145 Mar 31); additional 2B/2B floorplans also listed</t>
+        </is>
+      </c>
+      <c r="L7" s="2" t="inlineStr">
+        <is>
+          <t>Up to 8 weeks free base rent</t>
+        </is>
+      </c>
+      <c r="M7" s="2" t="n"/>
+      <c r="N7" s="2" t="inlineStr">
+        <is>
+          <t>Minimum lease term applies</t>
+        </is>
+      </c>
+      <c r="O7" s="2" t="inlineStr">
+        <is>
+          <t>5.0 (2 reviews)</t>
+        </is>
+      </c>
+      <c r="P7" s="3" t="inlineStr">
+        <is>
+          <t>https://sevensmv.com/</t>
+        </is>
+      </c>
+      <c r="Q7" s="3" t="inlineStr">
+        <is>
+          <t>https://www.apartments.com/sevens-mountain-view-ca/3rr7vmg/</t>
+        </is>
+      </c>
+      <c r="R7" s="2" t="inlineStr">
+        <is>
+          <t>Mountain View</t>
+        </is>
+      </c>
+      <c r="S7" s="2" t="inlineStr">
+        <is>
+          <t>~0.75 mi</t>
+        </is>
+      </c>
+      <c r="T7" s="2" t="inlineStr">
+        <is>
+          <t>15 min</t>
+        </is>
+      </c>
+      <c r="U7" s="2" t="inlineStr">
+        <is>
+          <t>At least one 2B/2B floorplan was available now and another set by Mar 31. Apartments.com labels pricing as total monthly price.</t>
+        </is>
+      </c>
+      <c r="V7" s="2" t="inlineStr">
+        <is>
+          <t>2026-03-17</t>
+        </is>
+      </c>
+      <c r="W7" s="2" t="inlineStr">
+        <is>
+          <t>Apartments.com live floor plan page</t>
+        </is>
+      </c>
+      <c r="X7" t="inlineStr">
+        <is>
+          <t>Official site lists a 15-minute walk; distance back-calculated at 20 min/mile</t>
+        </is>
+      </c>
+      <c r="Y7" t="inlineStr">
+        <is>
+          <t>In-unit washer/dryer</t>
+        </is>
+      </c>
+      <c r="Z7" t="inlineStr">
+        <is>
+          <t>Official amenities page lists In-Unit Washer and Dryer; Apartments.com and Zillow also list in-unit washer/dryer.</t>
+        </is>
+      </c>
+      <c r="AA7" t="inlineStr">
+        <is>
+          <t>Official site states Mountain View Caltrain Station is a 15-minute walk from Sevens and lists in-unit washer/dryer.</t>
+        </is>
+      </c>
+      <c r="AB7" t="inlineStr">
+        <is>
+          <t>https://sevensmv.com/amenities/
+https://sevensmv.com/p/transportation/
+https://www.apartments.com/sevens-mountain-view-ca/3rr7vmg/
+https://www.zillow.com/apartments/mountain-view-ca/sevens/9VG5jp/</t>
+        </is>
+      </c>
+      <c r="AC7" t="inlineStr">
+        <is>
+          <t>2026-03-18</t>
+        </is>
+      </c>
+      <c r="AD7" t="n">
+        <v>0.91</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="2" t="inlineStr">
+        <is>
+          <t>The Dean</t>
+        </is>
+      </c>
+      <c r="B8" s="2" t="inlineStr">
+        <is>
+          <t>Mountain View</t>
+        </is>
+      </c>
+      <c r="C8" s="2" t="inlineStr">
+        <is>
+          <t>ELIGIBLE</t>
+        </is>
+      </c>
+      <c r="D8" s="2" t="inlineStr">
+        <is>
+          <t>Now</t>
+        </is>
+      </c>
+      <c r="E8" s="2" t="inlineStr">
+        <is>
+          <t>2026-04-10</t>
+        </is>
+      </c>
+      <c r="F8" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="G8" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="H8" s="2" t="inlineStr">
+        <is>
+          <t>951-1,142</t>
+        </is>
+      </c>
+      <c r="I8" s="2" t="inlineStr">
+        <is>
+          <t>$5,646+</t>
+        </is>
+      </c>
+      <c r="J8" s="2" t="inlineStr">
+        <is>
+          <t>Base rent</t>
+        </is>
+      </c>
+      <c r="K8" s="2" t="inlineStr">
+        <is>
+          <t>2A (Units 1224, 1724 now); 2G (Units 4134, 4130, 3107 now); 2H (Unit 3205 now)</t>
+        </is>
+      </c>
+      <c r="L8" s="2" t="inlineStr">
+        <is>
+          <t>2 weeks free on select apartments</t>
+        </is>
+      </c>
+      <c r="M8" s="2" t="inlineStr">
+        <is>
+          <t>$500</t>
+        </is>
+      </c>
+      <c r="N8" s="2" t="inlineStr">
+        <is>
+          <t>Month-to-month and short-term leases available</t>
+        </is>
+      </c>
+      <c r="O8" s="2" t="inlineStr">
+        <is>
+          <t>4.8 (3 reviews)</t>
+        </is>
+      </c>
+      <c r="P8" s="3" t="inlineStr">
+        <is>
+          <t>https://prometheusapartments.com/ca/mountain-view-apartments/the-dean</t>
+        </is>
+      </c>
+      <c r="Q8" s="3" t="inlineStr">
+        <is>
+          <t>https://www.apartments.com/dean-mountain-view-ca/3yxd35f/</t>
+        </is>
+      </c>
+      <c r="R8" s="2" t="inlineStr">
+        <is>
+          <t>San Antonio</t>
+        </is>
+      </c>
+      <c r="S8" s="2" t="inlineStr">
+        <is>
+          <t>0.5 mi</t>
+        </is>
+      </c>
+      <c r="T8" s="2" t="inlineStr">
+        <is>
+          <t>9 min</t>
+        </is>
+      </c>
+      <c r="U8" s="2" t="inlineStr">
+        <is>
+          <t>Multiple live 2B/2B floorplans were posted on March 18, 2026; this is one of the closest San Antonio-area additions.</t>
+        </is>
+      </c>
+      <c r="V8" s="2" t="inlineStr">
+        <is>
+          <t>2026-03-18</t>
+        </is>
+      </c>
+      <c r="W8" s="2" t="inlineStr">
+        <is>
+          <t>Apartments.com exact property page plus Prometheus official page</t>
+        </is>
+      </c>
+      <c r="X8" t="inlineStr">
+        <is>
+          <t>Listed walking time/distance from Apartments.com transportation section</t>
+        </is>
+      </c>
+      <c r="Y8" t="inlineStr">
+        <is>
+          <t>In-unit washer/dryer</t>
+        </is>
+      </c>
+      <c r="Z8" t="inlineStr">
+        <is>
+          <t>Apartments.com lists Washer/Dryer in apartment features, and the official community markets in-home laundry among its residential finishes.</t>
+        </is>
+      </c>
+      <c r="AA8" t="inlineStr">
+        <is>
+          <t>Apartments.com shows San Antonio Caltrain as a 0.5-mile, 9-minute walk and lists Washer/Dryer in unit features. Prometheus is the official site of record.</t>
+        </is>
+      </c>
+      <c r="AB8" t="inlineStr">
+        <is>
+          <t>https://prometheusapartments.com/ca/mountain-view-apartments/the-dean
+https://www.apartments.com/dean-mountain-view-ca/3yxd35f/
+https://www.apartmenthomeliving.com/mountain-view-ca/apartments-for-rent/2-bedroom</t>
+        </is>
+      </c>
+      <c r="AC8" t="inlineStr">
+        <is>
+          <t>2026-03-18</t>
+        </is>
+      </c>
+      <c r="AD8" t="n">
+        <v>0.95</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="2" t="inlineStr">
+        <is>
+          <t>The Shadows Apartments</t>
+        </is>
+      </c>
+      <c r="B9" s="2" t="inlineStr">
+        <is>
+          <t>Mountain View</t>
+        </is>
+      </c>
+      <c r="C9" s="2" t="inlineStr">
+        <is>
+          <t>ELIGIBLE</t>
+        </is>
+      </c>
+      <c r="D9" s="2" t="inlineStr">
+        <is>
+          <t>Now</t>
+        </is>
+      </c>
+      <c r="E9" s="2" t="inlineStr">
+        <is>
+          <t>2026-04-10</t>
+        </is>
+      </c>
+      <c r="F9" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="G9" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="H9" s="2" t="inlineStr">
+        <is>
+          <t>1,025</t>
+        </is>
+      </c>
+      <c r="I9" s="2" t="inlineStr">
+        <is>
+          <t>$4,595</t>
+        </is>
+      </c>
+      <c r="J9" s="2" t="inlineStr">
+        <is>
+          <t>Base rent</t>
+        </is>
+      </c>
+      <c r="K9" s="2" t="inlineStr">
+        <is>
+          <t>E floorplan</t>
+        </is>
+      </c>
+      <c r="L9" s="2" t="inlineStr">
+        <is>
+          <t>$1,000 off when you look and lease; water, sewer, and garbage included in rent</t>
+        </is>
+      </c>
+      <c r="M9" s="2" t="inlineStr">
+        <is>
+          <t>$800</t>
+        </is>
+      </c>
+      <c r="N9" s="2" t="n"/>
+      <c r="O9" s="2" t="inlineStr">
+        <is>
+          <t>4.0 (0 reviews)</t>
+        </is>
+      </c>
+      <c r="P9" s="3" t="inlineStr">
+        <is>
+          <t>https://www.shadowsapartments.com/</t>
+        </is>
+      </c>
+      <c r="Q9" s="3" t="inlineStr">
+        <is>
+          <t>https://www.apartments.com/the-shadows-apartments-mountain-view-ca/ysm3jjr/</t>
+        </is>
+      </c>
+      <c r="R9" s="2" t="inlineStr">
+        <is>
+          <t>Mountain View</t>
+        </is>
+      </c>
+      <c r="S9" s="2" t="inlineStr">
+        <is>
+          <t>1.0 mi</t>
+        </is>
+      </c>
+      <c r="T9" s="2" t="inlineStr">
+        <is>
+          <t>18 min</t>
+        </is>
+      </c>
+      <c r="U9" s="2" t="inlineStr">
+        <is>
+          <t>The 2B/2B floorplan was listed as available now without individual unit rows on Apartments.com.</t>
+        </is>
+      </c>
+      <c r="V9" s="2" t="inlineStr">
+        <is>
+          <t>2026-03-17</t>
+        </is>
+      </c>
+      <c r="W9" s="2" t="inlineStr">
+        <is>
+          <t>Apartments.com live floor plan page</t>
+        </is>
+      </c>
+      <c r="X9" t="inlineStr">
+        <is>
+          <t>Reported walking time from property transit listing</t>
+        </is>
+      </c>
+      <c r="Y9" t="inlineStr">
+        <is>
+          <t>In-unit washer/dryer</t>
+        </is>
+      </c>
+      <c r="Z9" t="inlineStr">
+        <is>
+          <t>Official site and Apartments.com both list in-unit washer/dryer; Apartments.com also lists shared laundry facilities in the community.</t>
+        </is>
+      </c>
+      <c r="AA9" t="inlineStr">
+        <is>
+          <t>Official site and Apartments.com identify The Shadows at 750 N Shoreline Blvd and both list in-unit washer/dryer. LoopNet shows Mountain View Caltrain at 1.0 mi / 18 min walk.</t>
+        </is>
+      </c>
+      <c r="AB9" t="inlineStr">
+        <is>
+          <t>https://www.shadowsapartments.com/
+https://www.apartments.com/the-shadows-apartments-mountain-view-ca/ysm3jjr/
+https://www.loopnet.com/property/750-n-shoreline-blvd-mountain-view-ca-94043/06085-15031038/
+https://www.caltrain.com/station/mountainview</t>
+        </is>
+      </c>
+      <c r="AC9" t="inlineStr">
+        <is>
+          <t>2026-03-18</t>
+        </is>
+      </c>
+      <c r="AD9" t="n">
+        <v>0.87</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="2" t="inlineStr">
+        <is>
+          <t>The Tillery</t>
+        </is>
+      </c>
+      <c r="B10" s="2" t="inlineStr">
+        <is>
+          <t>Mountain View</t>
+        </is>
+      </c>
+      <c r="C10" s="2" t="inlineStr">
+        <is>
+          <t>ELIGIBLE</t>
+        </is>
+      </c>
+      <c r="D10" s="2" t="inlineStr">
+        <is>
+          <t>Now</t>
+        </is>
+      </c>
+      <c r="E10" s="2" t="inlineStr">
+        <is>
+          <t>2026-04-10</t>
+        </is>
+      </c>
+      <c r="F10" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="G10" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="H10" s="2" t="inlineStr">
+        <is>
+          <t>1,194-1,232</t>
+        </is>
+      </c>
+      <c r="I10" s="2" t="inlineStr">
+        <is>
+          <t>$5,023-$6,098</t>
+        </is>
+      </c>
+      <c r="J10" s="2" t="inlineStr">
+        <is>
+          <t>Base rent</t>
+        </is>
+      </c>
+      <c r="K10" s="2" t="inlineStr">
+        <is>
+          <t>2A (Units 202, 402 now); 2C (Units 204, 404 now); 2D (Units 201, 203, 301 now)</t>
+        </is>
+      </c>
+      <c r="L10" s="2" t="inlineStr">
+        <is>
+          <t>Save up to 4 weeks</t>
+        </is>
+      </c>
+      <c r="M10" s="2" t="inlineStr">
+        <is>
+          <t>$500</t>
+        </is>
+      </c>
+      <c r="N10" s="2" t="n"/>
+      <c r="O10" s="2" t="inlineStr">
+        <is>
+          <t>5.0 (0 reviews)</t>
+        </is>
+      </c>
+      <c r="P10" s="3" t="inlineStr">
+        <is>
+          <t>https://prometheusapartments.com/ca/mountain-view-apartments/the-tillery</t>
+        </is>
+      </c>
+      <c r="Q10" s="3" t="inlineStr">
+        <is>
+          <t>https://www.apartments.com/the-tillery-mountain-view-ca/yr0kvys/</t>
+        </is>
+      </c>
+      <c r="R10" s="2" t="inlineStr">
+        <is>
+          <t>Mountain View</t>
+        </is>
+      </c>
+      <c r="S10" s="2" t="inlineStr">
+        <is>
+          <t>1.0 mi</t>
+        </is>
+      </c>
+      <c r="T10" s="2" t="inlineStr">
+        <is>
+          <t>19 min</t>
+        </is>
+      </c>
+      <c r="U10" s="2" t="inlineStr">
+        <is>
+          <t>The Tillery is current and walkable to Mountain View Caltrain, but it sits at the high end of your search budget.</t>
+        </is>
+      </c>
+      <c r="V10" s="2" t="inlineStr">
+        <is>
+          <t>2026-03-18</t>
+        </is>
+      </c>
+      <c r="W10" s="2" t="inlineStr">
+        <is>
+          <t>Apartments.com exact property page plus ApartmentHomeLiving 2-bedroom availability</t>
+        </is>
+      </c>
+      <c r="X10" t="inlineStr">
+        <is>
+          <t>Listed walking time/distance from Apartments.com transportation section</t>
+        </is>
+      </c>
+      <c r="Y10" t="inlineStr">
+        <is>
+          <t>In-unit washer/dryer</t>
+        </is>
+      </c>
+      <c r="Z10" t="inlineStr">
+        <is>
+          <t>Apartments.com lists stackable Washer &amp; Dryer as a unique feature.</t>
+        </is>
+      </c>
+      <c r="AA10" t="inlineStr">
+        <is>
+          <t>Apartments.com shows Mountain View Caltrain as a 1.0-mile, 19-minute walk and identifies stackable Washer &amp; Dryer as a unit feature.</t>
+        </is>
+      </c>
+      <c r="AB10" t="inlineStr">
+        <is>
+          <t>https://prometheusapartments.com/ca/mountain-view-apartments/the-tillery
+https://www.apartments.com/the-tillery-mountain-view-ca/yr0kvys/
+https://www.apartmenthomeliving.com/mountain-view-ca/apartments-for-rent/2-bedroom</t>
+        </is>
+      </c>
+      <c r="AC10" t="inlineStr">
+        <is>
+          <t>2026-03-18</t>
+        </is>
+      </c>
+      <c r="AD10" t="n">
+        <v>0.9399999999999999</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="2" t="inlineStr">
+        <is>
+          <t>Verve</t>
+        </is>
+      </c>
+      <c r="B11" s="2" t="inlineStr">
+        <is>
+          <t>Mountain View</t>
+        </is>
+      </c>
+      <c r="C11" s="2" t="inlineStr">
+        <is>
+          <t>ELIGIBLE</t>
+        </is>
+      </c>
+      <c r="D11" s="2" t="inlineStr">
+        <is>
+          <t>Now</t>
+        </is>
+      </c>
+      <c r="E11" s="2" t="inlineStr">
+        <is>
+          <t>2026-04-10</t>
+        </is>
+      </c>
+      <c r="F11" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="G11" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="H11" s="2" t="inlineStr">
+        <is>
+          <t>1,121-1,651</t>
+        </is>
+      </c>
+      <c r="I11" s="2" t="inlineStr">
+        <is>
+          <t>$5,139-$5,736</t>
+        </is>
+      </c>
+      <c r="J11" s="2" t="inlineStr">
+        <is>
+          <t>Base rent</t>
+        </is>
+      </c>
+      <c r="K11" s="2" t="inlineStr">
+        <is>
+          <t>B2A / Unit 322 now; B2G / Unit 410 Mar 27</t>
+        </is>
+      </c>
+      <c r="L11" s="2" t="n"/>
+      <c r="M11" s="2" t="n"/>
+      <c r="N11" s="2" t="n"/>
+      <c r="O11" s="2" t="inlineStr">
+        <is>
+          <t>4.0 (0 reviews)</t>
+        </is>
+      </c>
+      <c r="P11" s="3" t="inlineStr">
+        <is>
+          <t>https://www.udr.com/san-francisco-bay-area-apartments/mountain-view/verve/amenities/</t>
+        </is>
+      </c>
+      <c r="Q11" s="3" t="inlineStr">
+        <is>
+          <t>https://www.apartments.com/verve-mountain-view-ca/dfw92yk/</t>
+        </is>
+      </c>
+      <c r="R11" s="2" t="inlineStr">
+        <is>
+          <t>San Antonio</t>
+        </is>
+      </c>
+      <c r="S11" s="2" t="inlineStr">
+        <is>
+          <t>0.66 mi</t>
+        </is>
+      </c>
+      <c r="T11" s="2" t="inlineStr">
+        <is>
+          <t>13 min</t>
+        </is>
+      </c>
+      <c r="U11" s="2" t="inlineStr">
+        <is>
+          <t>Another 2B/2B unit (B2J / Unit 412) was listed for Apr 23 and excluded from the eligible interpretation.</t>
+        </is>
+      </c>
+      <c r="V11" s="2" t="inlineStr">
+        <is>
+          <t>2026-03-17</t>
+        </is>
+      </c>
+      <c r="W11" s="2" t="inlineStr">
+        <is>
+          <t>Apartments.com live floor plan page</t>
+        </is>
+      </c>
+      <c r="X11" t="inlineStr">
+        <is>
+          <t>Estimated from listed distance at 20 min/mile because no explicit walking time was published</t>
+        </is>
+      </c>
+      <c r="Y11" t="inlineStr">
+        <is>
+          <t>In-unit washer/dryer</t>
+        </is>
+      </c>
+      <c r="Z11" t="inlineStr">
+        <is>
+          <t>Official UDR amenities page says in-home washer/dryer; Apartments.com and ApartmentHomeLiving also list in-unit Washer/Dryer.</t>
+        </is>
+      </c>
+      <c r="AA11" t="inlineStr">
+        <is>
+          <t>Official UDR pages say Verve has an in-home washer/dryer. ApartmentHomeLiving lists San Antonio Caltrain as the closest stop at 0.66 mi.</t>
+        </is>
+      </c>
+      <c r="AB11" t="inlineStr">
+        <is>
+          <t>https://www.udr.com/san-francisco-bay-area-apartments/mountain-view/verve/neighborhood/
+https://www.apartments.com/verve-mountain-view-ca/dfw92yk/
+https://www.apartmenthomeliving.com/apartment-finder/Verve-Mountain-View-CA-94040-3051240
+https://www.caltrain.com/station/sanantonio</t>
+        </is>
+      </c>
+      <c r="AC11" t="inlineStr">
+        <is>
+          <t>2026-03-18</t>
+        </is>
+      </c>
+      <c r="AD11" t="n">
+        <v>0.79</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="2" t="inlineStr">
+        <is>
+          <t>345 Sheridan Ave Unit SI FL3-ID806</t>
+        </is>
+      </c>
+      <c r="B12" s="2" t="inlineStr">
+        <is>
+          <t>Palo Alto</t>
+        </is>
+      </c>
+      <c r="C12" s="2" t="inlineStr">
+        <is>
+          <t>ELIGIBLE</t>
+        </is>
+      </c>
+      <c r="D12" s="2" t="inlineStr">
+        <is>
+          <t>2026-03-18</t>
+        </is>
+      </c>
+      <c r="E12" s="2" t="inlineStr">
+        <is>
+          <t>2026-04-10</t>
+        </is>
+      </c>
+      <c r="F12" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="G12" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="H12" s="2" t="inlineStr">
+        <is>
+          <t>1,097</t>
+        </is>
+      </c>
+      <c r="I12" s="2" t="inlineStr">
+        <is>
+          <t>$4,090 lowest advertised; $4,400 for 1-year stay</t>
+        </is>
+      </c>
+      <c r="J12" s="2" t="inlineStr">
+        <is>
+          <t>Term-dependent furnished rate</t>
+        </is>
+      </c>
+      <c r="K12" s="2" t="inlineStr">
+        <is>
+          <t>Blueground unit SI FL3-ID806</t>
+        </is>
+      </c>
+      <c r="L12" s="2" t="n"/>
+      <c r="M12" s="2" t="n"/>
+      <c r="N12" s="2" t="inlineStr">
+        <is>
+          <t>1-12 months</t>
+        </is>
+      </c>
+      <c r="O12" s="2" t="inlineStr">
+        <is>
+          <t>n/a on unit listing</t>
+        </is>
+      </c>
+      <c r="P12" s="3" t="inlineStr">
+        <is>
+          <t>https://www.theblueground.com/p/furnished-apartments/sfo-806?utm_campaign=SFO&amp;utm_medium=Feed&amp;utm_source=apartments</t>
+        </is>
+      </c>
+      <c r="Q12" s="3" t="inlineStr">
+        <is>
+          <t>https://www.apartments.com/345-sheridan-ave-palo-alto-ca-unit-si-fl3-id806/rhckc00/</t>
+        </is>
+      </c>
+      <c r="R12" s="2" t="inlineStr">
+        <is>
+          <t>California Ave</t>
+        </is>
+      </c>
+      <c r="S12" s="2" t="inlineStr">
+        <is>
+          <t>0.4 mi</t>
+        </is>
+      </c>
+      <c r="T12" s="2" t="inlineStr">
+        <is>
+          <t>8 min</t>
+        </is>
+      </c>
+      <c r="U12" s="2" t="inlineStr">
+        <is>
+          <t>Furnished Blueground unit. Lowest rate depends on stay length; 1-year pricing was explicitly listed at $4,400/month.</t>
+        </is>
+      </c>
+      <c r="V12" s="2" t="inlineStr">
+        <is>
+          <t>2026-03-17</t>
+        </is>
+      </c>
+      <c r="W12" s="2" t="inlineStr">
+        <is>
+          <t>Apartments.com unit page</t>
+        </is>
+      </c>
+      <c r="X12" t="inlineStr">
+        <is>
+          <t>Listed walk time on Apartments.com</t>
+        </is>
+      </c>
+      <c r="Y12" t="inlineStr">
+        <is>
+          <t>In-unit washer/dryer</t>
+        </is>
+      </c>
+      <c r="Z12" t="inlineStr">
+        <is>
+          <t>Apartments.com says the apartment offers in-apartment laundry and lists Washer/Dryer in features.</t>
+        </is>
+      </c>
+      <c r="AA12" t="inlineStr">
+        <is>
+          <t>Apartments.com lists California Avenue Caltrain at 0.4 mi / 8 min walk and states the apartment has in-apartment laundry with washer/dryer.</t>
+        </is>
+      </c>
+      <c r="AB12" t="inlineStr">
+        <is>
+          <t>https://www.apartments.com/345-sheridan-ave-palo-alto-ca-unit-si-fl3-id806/rhckc00/
+https://www.theblueground.com/m/furnished-apartments/palo-alto-ca-usa/f/bedrooms-2</t>
+        </is>
+      </c>
+      <c r="AC12" t="inlineStr">
+        <is>
+          <t>2026-03-18</t>
+        </is>
+      </c>
+      <c r="AD12" t="n">
+        <v>0.9</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="2" t="inlineStr">
+        <is>
           <t>Montage Apartments</t>
         </is>
       </c>
-      <c r="B3" s="2" t="inlineStr">
+      <c r="B13" s="2" t="inlineStr">
         <is>
           <t>Palo Alto</t>
         </is>
       </c>
-      <c r="C3" s="2" t="inlineStr">
+      <c r="C13" s="2" t="inlineStr">
         <is>
           <t>ELIGIBLE</t>
         </is>
       </c>
-      <c r="D3" s="2" t="inlineStr">
+      <c r="D13" s="2" t="inlineStr">
         <is>
           <t>Now</t>
         </is>
       </c>
-      <c r="E3" s="2" t="inlineStr">
+      <c r="E13" s="2" t="inlineStr">
         <is>
           <t>2026-04-10</t>
         </is>
       </c>
-      <c r="F3" s="2" t="inlineStr">
+      <c r="F13" s="2" t="inlineStr">
         <is>
           <t>2</t>
         </is>
       </c>
-      <c r="G3" s="2" t="inlineStr">
+      <c r="G13" s="2" t="inlineStr">
         <is>
           <t>2</t>
         </is>
       </c>
-      <c r="H3" s="2" t="inlineStr">
+      <c r="H13" s="2" t="inlineStr">
         <is>
           <t>1,000</t>
         </is>
       </c>
-      <c r="I3" s="2" t="inlineStr">
+      <c r="I13" s="2" t="inlineStr">
         <is>
           <t>$4,995</t>
         </is>
       </c>
-      <c r="J3" s="2" t="inlineStr">
+      <c r="J13" s="2" t="inlineStr">
         <is>
           <t>Base rent</t>
         </is>
       </c>
-      <c r="K3" s="2" t="inlineStr">
+      <c r="K13" s="2" t="inlineStr">
         <is>
           <t>NEWLY REMODELED Upstairs 2BRx2BA</t>
         </is>
       </c>
-      <c r="L3" s="2" t="inlineStr">
+      <c r="L13" s="2" t="inlineStr">
         <is>
           <t>One month free with a 15-month lease and immediate move-in</t>
         </is>
       </c>
-      <c r="M3" s="2" t="inlineStr">
+      <c r="M13" s="2" t="inlineStr">
         <is>
           <t>$1,000</t>
         </is>
       </c>
-      <c r="N3" s="2" t="inlineStr">
+      <c r="N13" s="2" t="inlineStr">
         <is>
           <t>15 months for special</t>
         </is>
       </c>
-      <c r="O3" s="2" t="inlineStr">
+      <c r="O13" s="2" t="inlineStr">
         <is>
           <t>4.0 (0 reviews)</t>
         </is>
       </c>
-      <c r="P3" s="2" t="inlineStr">
+      <c r="P13" s="3" t="inlineStr">
         <is>
           <t>https://montagebayarea.com/</t>
         </is>
       </c>
-      <c r="Q3" s="3" t="inlineStr">
+      <c r="Q13" s="3" t="inlineStr">
         <is>
           <t>https://www.apartments.com/montage-apartments-palo-alto-ca/fqckbxs/</t>
         </is>
       </c>
-      <c r="R3" s="2" t="inlineStr">
+      <c r="R13" s="2" t="inlineStr">
         <is>
           <t>California Ave</t>
         </is>
       </c>
-      <c r="S3" s="2" t="inlineStr">
+      <c r="S13" s="2" t="inlineStr">
         <is>
           <t>0.8 mi</t>
         </is>
       </c>
-      <c r="T3" s="2" t="inlineStr">
+      <c r="T13" s="2" t="inlineStr">
         <is>
           <t>15 min</t>
         </is>
       </c>
-      <c r="U3" s="2" t="inlineStr">
+      <c r="U13" s="2" t="inlineStr">
         <is>
           <t>Single 2B/2B floorplan listed as available now.</t>
         </is>
       </c>
-      <c r="V3" s="2" t="inlineStr">
+      <c r="V13" s="2" t="inlineStr">
         <is>
           <t>2026-03-17</t>
         </is>
       </c>
-      <c r="W3" s="2" t="inlineStr">
+      <c r="W13" s="2" t="inlineStr">
         <is>
           <t>Apartments.com live floor plan page</t>
         </is>
       </c>
-      <c r="X3" t="inlineStr">
+      <c r="X13" t="inlineStr">
         <is>
           <t>Listed walking time/distance from third-party map result</t>
         </is>
       </c>
-      <c r="Y3" t="inlineStr">
+      <c r="Y13" t="inlineStr">
         <is>
           <t>In-unit washer/dryer</t>
         </is>
       </c>
-      <c r="Z3" t="inlineStr">
+      <c r="Z13" t="inlineStr">
         <is>
           <t>Official site says in-home washer/dryers and washer/dryer in every home; Apartments.com also lists Washer/Dryer.</t>
         </is>
       </c>
-      <c r="AA3" t="inlineStr">
+      <c r="AA13" t="inlineStr">
         <is>
           <t>Official site and Apartments.com both confirm in-unit washer/dryer. California Ave is the nearest Caltrain stop; LoopNet listed it at 0.8 mi / 15 min walk.</t>
         </is>
       </c>
-      <c r="AB3" t="inlineStr">
+      <c r="AB13" t="inlineStr">
         <is>
           <t>https://montagebayarea.com/
 https://www.apartments.com/montage-apartments-palo-alto-ca/fqckbxs/
@@ -919,144 +2369,144 @@
 https://www.loopnet.com/property/el-camino-real-palo-alto-ca-94306/06085-14220079/</t>
         </is>
       </c>
-      <c r="AC3" t="inlineStr">
+      <c r="AC13" t="inlineStr">
         <is>
           <t>2026-03-18</t>
         </is>
       </c>
-      <c r="AD3" t="n">
+      <c r="AD13" t="n">
         <v>0.77</v>
       </c>
     </row>
-    <row r="4">
-      <c r="A4" s="2" t="inlineStr">
+    <row r="14">
+      <c r="A14" s="2" t="inlineStr">
         <is>
           <t>Southwood Apartments</t>
         </is>
       </c>
-      <c r="B4" s="2" t="inlineStr">
+      <c r="B14" s="2" t="inlineStr">
         <is>
           <t>Palo Alto</t>
         </is>
       </c>
-      <c r="C4" s="2" t="inlineStr">
+      <c r="C14" s="2" t="inlineStr">
         <is>
           <t>ELIGIBLE</t>
         </is>
       </c>
-      <c r="D4" s="2" t="inlineStr">
+      <c r="D14" s="2" t="inlineStr">
         <is>
           <t>2026-04-10</t>
         </is>
       </c>
-      <c r="E4" s="2" t="inlineStr">
+      <c r="E14" s="2" t="inlineStr">
         <is>
           <t>2026-04-10</t>
         </is>
       </c>
-      <c r="F4" s="2" t="inlineStr">
+      <c r="F14" s="2" t="inlineStr">
         <is>
           <t>2</t>
         </is>
       </c>
-      <c r="G4" s="2" t="inlineStr">
+      <c r="G14" s="2" t="inlineStr">
         <is>
           <t>2</t>
         </is>
       </c>
-      <c r="H4" s="2" t="inlineStr">
+      <c r="H14" s="2" t="inlineStr">
         <is>
           <t>980</t>
         </is>
       </c>
-      <c r="I4" s="2" t="inlineStr">
+      <c r="I14" s="2" t="inlineStr">
         <is>
           <t>$4,195</t>
         </is>
       </c>
-      <c r="J4" s="2" t="inlineStr">
+      <c r="J14" s="2" t="inlineStr">
         <is>
           <t>Base rent</t>
         </is>
       </c>
-      <c r="K4" s="2" t="inlineStr">
+      <c r="K14" s="2" t="inlineStr">
         <is>
           <t>2x2A / Unit 113</t>
         </is>
       </c>
-      <c r="L4" s="2" t="inlineStr"/>
-      <c r="M4" s="2" t="inlineStr">
+      <c r="L14" s="2" t="n"/>
+      <c r="M14" s="2" t="inlineStr">
         <is>
           <t>$1,000</t>
         </is>
       </c>
-      <c r="N4" s="2" t="inlineStr"/>
-      <c r="O4" s="2" t="inlineStr">
+      <c r="N14" s="2" t="n"/>
+      <c r="O14" s="2" t="inlineStr">
         <is>
           <t>3.9 (1 review)</t>
         </is>
       </c>
-      <c r="P4" s="3" t="inlineStr">
+      <c r="P14" s="3" t="inlineStr">
         <is>
           <t>https://www.southwood-apartments.com/</t>
         </is>
       </c>
-      <c r="Q4" s="3" t="inlineStr">
+      <c r="Q14" s="3" t="inlineStr">
         <is>
           <t>https://www.apartments.com/southwood-apartments-palo-alto-ca/6f8zpmt/</t>
         </is>
       </c>
-      <c r="R4" s="2" t="inlineStr">
+      <c r="R14" s="2" t="inlineStr">
         <is>
           <t>California Ave</t>
         </is>
       </c>
-      <c r="S4" s="2" t="inlineStr">
+      <c r="S14" s="2" t="inlineStr">
         <is>
           <t>1.3 mi</t>
         </is>
       </c>
-      <c r="T4" s="2" t="inlineStr">
+      <c r="T14" s="2" t="inlineStr">
         <is>
           <t>26 min</t>
         </is>
       </c>
-      <c r="U4" s="2" t="inlineStr">
+      <c r="U14" s="2" t="inlineStr">
         <is>
           <t>Only one 2B/2B unit was live and it becomes available on April 10, 2026.</t>
         </is>
       </c>
-      <c r="V4" s="2" t="inlineStr">
+      <c r="V14" s="2" t="inlineStr">
         <is>
           <t>2026-03-17</t>
         </is>
       </c>
-      <c r="W4" s="2" t="inlineStr">
+      <c r="W14" s="2" t="inlineStr">
         <is>
           <t>Apartments.com live floor plan page</t>
         </is>
       </c>
-      <c r="X4" t="inlineStr">
+      <c r="X14" t="inlineStr">
         <is>
           <t>Estimated from walking distance at 20 min/mile using map/search distance</t>
         </is>
       </c>
-      <c r="Y4" t="inlineStr">
+      <c r="Y14" t="inlineStr">
         <is>
           <t>In-unit washer/dryer</t>
         </is>
       </c>
-      <c r="Z4" t="inlineStr">
+      <c r="Z14" t="inlineStr">
         <is>
           <t>Official site says homes feature in-home washers and dryers, and Apartments.com also lists Washer/Dryer in apartment features.</t>
         </is>
       </c>
-      <c r="AA4" t="inlineStr">
+      <c r="AA14" t="inlineStr">
         <is>
           <t>Official site confirms in-home washer/dryer. Listing sites did not provide a walk route, so the California Ave walk time was estimated from map/search distance.</t>
         </is>
       </c>
-      <c r="AB4" t="inlineStr">
+      <c r="AB14" t="inlineStr">
         <is>
           <t>https://www.southwood-apartments.com/
 https://www.southwood-apartments.com/floorplans/one-bedroom-one-bathroom
@@ -1065,1461 +2515,24 @@
 https://www.walkscore.com/score/middlefield-rd-and-colorado-ave-palo-alto-ca-94306</t>
         </is>
       </c>
-      <c r="AC4" t="inlineStr">
+      <c r="AC14" t="inlineStr">
         <is>
           <t>2026-03-18</t>
         </is>
       </c>
-      <c r="AD4" t="n">
+      <c r="AD14" t="n">
         <v>0.74</v>
-      </c>
-    </row>
-    <row r="5">
-      <c r="A5" s="2" t="inlineStr">
-        <is>
-          <t>345 Sheridan Ave Unit SI FL3-ID806</t>
-        </is>
-      </c>
-      <c r="B5" s="2" t="inlineStr">
-        <is>
-          <t>Palo Alto</t>
-        </is>
-      </c>
-      <c r="C5" s="2" t="inlineStr">
-        <is>
-          <t>ELIGIBLE</t>
-        </is>
-      </c>
-      <c r="D5" s="2" t="inlineStr">
-        <is>
-          <t>2026-03-18</t>
-        </is>
-      </c>
-      <c r="E5" s="2" t="inlineStr">
-        <is>
-          <t>2026-04-10</t>
-        </is>
-      </c>
-      <c r="F5" s="2" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="G5" s="2" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="H5" s="2" t="inlineStr">
-        <is>
-          <t>1,097</t>
-        </is>
-      </c>
-      <c r="I5" s="2" t="inlineStr">
-        <is>
-          <t>$4,090 lowest advertised; $4,400 for 1-year stay</t>
-        </is>
-      </c>
-      <c r="J5" s="2" t="inlineStr">
-        <is>
-          <t>Term-dependent furnished rate</t>
-        </is>
-      </c>
-      <c r="K5" s="2" t="inlineStr">
-        <is>
-          <t>Blueground unit SI FL3-ID806</t>
-        </is>
-      </c>
-      <c r="L5" s="2" t="inlineStr"/>
-      <c r="M5" s="2" t="inlineStr"/>
-      <c r="N5" s="2" t="inlineStr">
-        <is>
-          <t>1-12 months</t>
-        </is>
-      </c>
-      <c r="O5" s="2" t="inlineStr">
-        <is>
-          <t>n/a on unit listing</t>
-        </is>
-      </c>
-      <c r="P5" s="3" t="inlineStr">
-        <is>
-          <t>https://www.theblueground.com/p/furnished-apartments/sfo-806?utm_campaign=SFO&amp;utm_medium=Feed&amp;utm_source=apartments</t>
-        </is>
-      </c>
-      <c r="Q5" s="3" t="inlineStr">
-        <is>
-          <t>https://www.apartments.com/345-sheridan-ave-palo-alto-ca-unit-si-fl3-id806/rhckc00/</t>
-        </is>
-      </c>
-      <c r="R5" s="2" t="inlineStr">
-        <is>
-          <t>California Ave</t>
-        </is>
-      </c>
-      <c r="S5" s="2" t="inlineStr">
-        <is>
-          <t>0.4 mi</t>
-        </is>
-      </c>
-      <c r="T5" s="2" t="inlineStr">
-        <is>
-          <t>8 min</t>
-        </is>
-      </c>
-      <c r="U5" s="2" t="inlineStr">
-        <is>
-          <t>Furnished Blueground unit. Lowest rate depends on stay length; 1-year pricing was explicitly listed at $4,400/month.</t>
-        </is>
-      </c>
-      <c r="V5" s="2" t="inlineStr">
-        <is>
-          <t>2026-03-17</t>
-        </is>
-      </c>
-      <c r="W5" s="2" t="inlineStr">
-        <is>
-          <t>Apartments.com unit page</t>
-        </is>
-      </c>
-      <c r="X5" t="inlineStr">
-        <is>
-          <t>Listed walk time on Apartments.com</t>
-        </is>
-      </c>
-      <c r="Y5" t="inlineStr">
-        <is>
-          <t>In-unit washer/dryer</t>
-        </is>
-      </c>
-      <c r="Z5" t="inlineStr">
-        <is>
-          <t>Apartments.com says the apartment offers in-apartment laundry and lists Washer/Dryer in features.</t>
-        </is>
-      </c>
-      <c r="AA5" t="inlineStr">
-        <is>
-          <t>Apartments.com lists California Avenue Caltrain at 0.4 mi / 8 min walk and states the apartment has in-apartment laundry with washer/dryer.</t>
-        </is>
-      </c>
-      <c r="AB5" t="inlineStr">
-        <is>
-          <t>https://www.apartments.com/345-sheridan-ave-palo-alto-ca-unit-si-fl3-id806/rhckc00/
-https://www.theblueground.com/m/furnished-apartments/palo-alto-ca-usa/f/bedrooms-2</t>
-        </is>
-      </c>
-      <c r="AC5" t="inlineStr">
-        <is>
-          <t>2026-03-18</t>
-        </is>
-      </c>
-      <c r="AD5" t="n">
-        <v>0.9</v>
-      </c>
-    </row>
-    <row r="6">
-      <c r="A6" s="2" t="inlineStr">
-        <is>
-          <t>Sevens</t>
-        </is>
-      </c>
-      <c r="B6" s="2" t="inlineStr">
-        <is>
-          <t>Mountain View</t>
-        </is>
-      </c>
-      <c r="C6" s="2" t="inlineStr">
-        <is>
-          <t>ELIGIBLE</t>
-        </is>
-      </c>
-      <c r="D6" s="2" t="inlineStr">
-        <is>
-          <t>Now</t>
-        </is>
-      </c>
-      <c r="E6" s="2" t="inlineStr">
-        <is>
-          <t>2026-04-10</t>
-        </is>
-      </c>
-      <c r="F6" s="2" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="G6" s="2" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="H6" s="2" t="inlineStr">
-        <is>
-          <t>1,021-1,240+</t>
-        </is>
-      </c>
-      <c r="I6" s="2" t="inlineStr">
-        <is>
-          <t>$5,979-$7,184</t>
-        </is>
-      </c>
-      <c r="J6" s="2" t="inlineStr">
-        <is>
-          <t>Total monthly price</t>
-        </is>
-      </c>
-      <c r="K6" s="2" t="inlineStr">
-        <is>
-          <t>B4 (Units B-130 now, B-276 now, B-176 Mar 31, B-145 Mar 31); additional 2B/2B floorplans also listed</t>
-        </is>
-      </c>
-      <c r="L6" s="2" t="inlineStr">
-        <is>
-          <t>Up to 8 weeks free base rent</t>
-        </is>
-      </c>
-      <c r="M6" s="2" t="inlineStr"/>
-      <c r="N6" s="2" t="inlineStr">
-        <is>
-          <t>Minimum lease term applies</t>
-        </is>
-      </c>
-      <c r="O6" s="2" t="inlineStr">
-        <is>
-          <t>5.0 (2 reviews)</t>
-        </is>
-      </c>
-      <c r="P6" s="2" t="inlineStr">
-        <is>
-          <t>https://sevensmv.com/</t>
-        </is>
-      </c>
-      <c r="Q6" s="3" t="inlineStr">
-        <is>
-          <t>https://www.apartments.com/sevens-mountain-view-ca/3rr7vmg/</t>
-        </is>
-      </c>
-      <c r="R6" s="2" t="inlineStr">
-        <is>
-          <t>Mountain View</t>
-        </is>
-      </c>
-      <c r="S6" s="2" t="inlineStr">
-        <is>
-          <t>~0.75 mi</t>
-        </is>
-      </c>
-      <c r="T6" s="2" t="inlineStr">
-        <is>
-          <t>15 min</t>
-        </is>
-      </c>
-      <c r="U6" s="2" t="inlineStr">
-        <is>
-          <t>At least one 2B/2B floorplan was available now and another set by Mar 31. Apartments.com labels pricing as total monthly price.</t>
-        </is>
-      </c>
-      <c r="V6" s="2" t="inlineStr">
-        <is>
-          <t>2026-03-17</t>
-        </is>
-      </c>
-      <c r="W6" s="2" t="inlineStr">
-        <is>
-          <t>Apartments.com live floor plan page</t>
-        </is>
-      </c>
-      <c r="X6" t="inlineStr">
-        <is>
-          <t>Official site lists a 15-minute walk; distance back-calculated at 20 min/mile</t>
-        </is>
-      </c>
-      <c r="Y6" t="inlineStr">
-        <is>
-          <t>In-unit washer/dryer</t>
-        </is>
-      </c>
-      <c r="Z6" t="inlineStr">
-        <is>
-          <t>Official amenities page lists In-Unit Washer and Dryer; Apartments.com and Zillow also list in-unit washer/dryer.</t>
-        </is>
-      </c>
-      <c r="AA6" t="inlineStr">
-        <is>
-          <t>Official site states Mountain View Caltrain Station is a 15-minute walk from Sevens and lists in-unit washer/dryer.</t>
-        </is>
-      </c>
-      <c r="AB6" t="inlineStr">
-        <is>
-          <t>https://sevensmv.com/amenities/
-https://sevensmv.com/p/transportation/
-https://www.apartments.com/sevens-mountain-view-ca/3rr7vmg/
-https://www.zillow.com/apartments/mountain-view-ca/sevens/9VG5jp/</t>
-        </is>
-      </c>
-      <c r="AC6" t="inlineStr">
-        <is>
-          <t>2026-03-18</t>
-        </is>
-      </c>
-      <c r="AD6" t="n">
-        <v>0.91</v>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7" s="2" t="inlineStr">
-        <is>
-          <t>Rowe at Pear Village</t>
-        </is>
-      </c>
-      <c r="B7" s="2" t="inlineStr">
-        <is>
-          <t>Mountain View</t>
-        </is>
-      </c>
-      <c r="C7" s="2" t="inlineStr">
-        <is>
-          <t>ELIGIBLE</t>
-        </is>
-      </c>
-      <c r="D7" s="2" t="inlineStr">
-        <is>
-          <t>2026-03-22</t>
-        </is>
-      </c>
-      <c r="E7" s="2" t="inlineStr">
-        <is>
-          <t>2026-04-10</t>
-        </is>
-      </c>
-      <c r="F7" s="2" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="G7" s="2" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="H7" s="2" t="inlineStr">
-        <is>
-          <t>1,146-1,318</t>
-        </is>
-      </c>
-      <c r="I7" s="2" t="inlineStr">
-        <is>
-          <t>$5,190-$5,650</t>
-        </is>
-      </c>
-      <c r="J7" s="2" t="inlineStr">
-        <is>
-          <t>Total monthly price</t>
-        </is>
-      </c>
-      <c r="K7" s="2" t="inlineStr">
-        <is>
-          <t>Unit 260 (1,146 sq ft, Mar 22); 2A.2 / Unit 332 (1,318 sq ft, Mar 25)</t>
-        </is>
-      </c>
-      <c r="L7" s="2" t="inlineStr"/>
-      <c r="M7" s="2" t="inlineStr"/>
-      <c r="N7" s="2" t="inlineStr"/>
-      <c r="O7" s="2" t="inlineStr">
-        <is>
-          <t>4.9 (11 reviews)</t>
-        </is>
-      </c>
-      <c r="P7" s="2" t="inlineStr">
-        <is>
-          <t>https://rowepearvillage.com/amenities/</t>
-        </is>
-      </c>
-      <c r="Q7" s="3" t="inlineStr">
-        <is>
-          <t>https://www.apartments.com/rowe-at-pear-village-mountain-view-ca/7fyfd6x/</t>
-        </is>
-      </c>
-      <c r="R7" s="2" t="inlineStr">
-        <is>
-          <t>Mountain View</t>
-        </is>
-      </c>
-      <c r="S7" s="2" t="inlineStr">
-        <is>
-          <t>1.13 mi</t>
-        </is>
-      </c>
-      <c r="T7" s="2" t="inlineStr">
-        <is>
-          <t>23 min</t>
-        </is>
-      </c>
-      <c r="U7" s="2" t="inlineStr">
-        <is>
-          <t>A May 7 unit was excluded from the eligible interpretation because it misses the early-April cutoff.</t>
-        </is>
-      </c>
-      <c r="V7" s="2" t="inlineStr">
-        <is>
-          <t>2026-03-17</t>
-        </is>
-      </c>
-      <c r="W7" s="2" t="inlineStr">
-        <is>
-          <t>Apartments.com live floor plan page</t>
-        </is>
-      </c>
-      <c r="X7" t="inlineStr">
-        <is>
-          <t>Estimated from the listed 1.13 mi distance at 20 min/mile</t>
-        </is>
-      </c>
-      <c r="Y7" t="inlineStr">
-        <is>
-          <t>In-unit washer/dryer</t>
-        </is>
-      </c>
-      <c r="Z7" t="inlineStr">
-        <is>
-          <t>Official site says Whirlpool front-load washer and dryer in unit; Apartments.com and Zillow also list in-unit laundry.</t>
-        </is>
-      </c>
-      <c r="AA7" t="inlineStr">
-        <is>
-          <t>Official amenities page lists in-unit washer/dryer. ApartmentHomeLiving lists Mountain View Caltrain at 1.13 mi; no direct walking route was exposed, so time was estimated.</t>
-        </is>
-      </c>
-      <c r="AB7" t="inlineStr">
-        <is>
-          <t>https://rowepearvillage.com/amenities/
-https://www.apartments.com/rowe-at-pear-village-mountain-view-ca/7fyfd6x/
-https://www.apartmenthomeliving.com/apartment-finder/Rowe-at-Pear-Village-Mountain-View-CA-94043-19859551
-https://www.caltrain.com/station/mountainview</t>
-        </is>
-      </c>
-      <c r="AC7" t="inlineStr">
-        <is>
-          <t>2026-03-18</t>
-        </is>
-      </c>
-      <c r="AD7" t="n">
-        <v>0.79</v>
-      </c>
-    </row>
-    <row r="8">
-      <c r="A8" s="2" t="inlineStr">
-        <is>
-          <t>Landsby</t>
-        </is>
-      </c>
-      <c r="B8" s="2" t="inlineStr">
-        <is>
-          <t>Mountain View</t>
-        </is>
-      </c>
-      <c r="C8" s="2" t="inlineStr">
-        <is>
-          <t>ELIGIBLE</t>
-        </is>
-      </c>
-      <c r="D8" s="2" t="inlineStr">
-        <is>
-          <t>Now</t>
-        </is>
-      </c>
-      <c r="E8" s="2" t="inlineStr">
-        <is>
-          <t>2026-04-10</t>
-        </is>
-      </c>
-      <c r="F8" s="2" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="G8" s="2" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="H8" s="2" t="inlineStr">
-        <is>
-          <t>964-1,047</t>
-        </is>
-      </c>
-      <c r="I8" s="2" t="inlineStr">
-        <is>
-          <t>$5,618-$5,710</t>
-        </is>
-      </c>
-      <c r="J8" s="2" t="inlineStr">
-        <is>
-          <t>Total monthly price</t>
-        </is>
-      </c>
-      <c r="K8" s="2" t="inlineStr">
-        <is>
-          <t>2A-6 / Unit 1511 now; 2K-1 / Unit 3521 Mar 21; 2B-1 / Unit 3319 Mar 23</t>
-        </is>
-      </c>
-      <c r="L8" s="2" t="inlineStr"/>
-      <c r="M8" s="2" t="inlineStr"/>
-      <c r="N8" s="2" t="inlineStr"/>
-      <c r="O8" s="2" t="inlineStr">
-        <is>
-          <t>4.6 (57 reviews)</t>
-        </is>
-      </c>
-      <c r="P8" s="2" t="inlineStr">
-        <is>
-          <t>https://livelandsby.com/</t>
-        </is>
-      </c>
-      <c r="Q8" s="3" t="inlineStr">
-        <is>
-          <t>https://www.apartments.com/landsby-mountain-view-ca/8mzlqg0/</t>
-        </is>
-      </c>
-      <c r="R8" s="2" t="inlineStr">
-        <is>
-          <t>San Antonio</t>
-        </is>
-      </c>
-      <c r="S8" s="2" t="inlineStr">
-        <is>
-          <t>0.2 mi</t>
-        </is>
-      </c>
-      <c r="T8" s="2" t="inlineStr">
-        <is>
-          <t>4 min</t>
-        </is>
-      </c>
-      <c r="U8" s="2" t="inlineStr">
-        <is>
-          <t>A second 2B-1 unit for May 8 was excluded from the eligible interpretation.</t>
-        </is>
-      </c>
-      <c r="V8" s="2" t="inlineStr">
-        <is>
-          <t>2026-03-17</t>
-        </is>
-      </c>
-      <c r="W8" s="2" t="inlineStr">
-        <is>
-          <t>Apartments.com live floor plan page</t>
-        </is>
-      </c>
-      <c r="X8" t="inlineStr">
-        <is>
-          <t>Listing-provided walking time</t>
-        </is>
-      </c>
-      <c r="Y8" t="inlineStr">
-        <is>
-          <t>In-unit washer/dryer</t>
-        </is>
-      </c>
-      <c r="Z8" t="inlineStr">
-        <is>
-          <t>Apartments.com says Landsby has in-unit washers/dryers; official amenities page lists a GE front-load washer &amp; dryer in select homes.</t>
-        </is>
-      </c>
-      <c r="AA8" t="inlineStr">
-        <is>
-          <t>Official site says Landsby is a short walk to San Antonio Caltrain; Apartments.com lists San Antonio at 0.2 mi / 4 min walk and confirms in-unit laundry.</t>
-        </is>
-      </c>
-      <c r="AB8" t="inlineStr">
-        <is>
-          <t>https://livelandsby.com/
-https://livelandsby.com/amenities/
-https://www.apartments.com/landsby-mountain-view-ca/8mzlqg0/</t>
-        </is>
-      </c>
-      <c r="AC8" t="inlineStr">
-        <is>
-          <t>2026-03-18</t>
-        </is>
-      </c>
-      <c r="AD8" t="n">
-        <v>0.97</v>
-      </c>
-    </row>
-    <row r="9">
-      <c r="A9" s="2" t="inlineStr">
-        <is>
-          <t>Verve</t>
-        </is>
-      </c>
-      <c r="B9" s="2" t="inlineStr">
-        <is>
-          <t>Mountain View</t>
-        </is>
-      </c>
-      <c r="C9" s="2" t="inlineStr">
-        <is>
-          <t>ELIGIBLE</t>
-        </is>
-      </c>
-      <c r="D9" s="2" t="inlineStr">
-        <is>
-          <t>Now</t>
-        </is>
-      </c>
-      <c r="E9" s="2" t="inlineStr">
-        <is>
-          <t>2026-04-10</t>
-        </is>
-      </c>
-      <c r="F9" s="2" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="G9" s="2" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="H9" s="2" t="inlineStr">
-        <is>
-          <t>1,121-1,651</t>
-        </is>
-      </c>
-      <c r="I9" s="2" t="inlineStr">
-        <is>
-          <t>$5,139-$5,736</t>
-        </is>
-      </c>
-      <c r="J9" s="2" t="inlineStr">
-        <is>
-          <t>Base rent</t>
-        </is>
-      </c>
-      <c r="K9" s="2" t="inlineStr">
-        <is>
-          <t>B2A / Unit 322 now; B2G / Unit 410 Mar 27</t>
-        </is>
-      </c>
-      <c r="L9" s="2" t="inlineStr"/>
-      <c r="M9" s="2" t="inlineStr"/>
-      <c r="N9" s="2" t="inlineStr"/>
-      <c r="O9" s="2" t="inlineStr">
-        <is>
-          <t>4.0 (0 reviews)</t>
-        </is>
-      </c>
-      <c r="P9" s="3" t="inlineStr">
-        <is>
-          <t>https://www.udr.com/san-francisco-bay-area-apartments/mountain-view/verve/amenities/</t>
-        </is>
-      </c>
-      <c r="Q9" s="3" t="inlineStr">
-        <is>
-          <t>https://www.apartments.com/verve-mountain-view-ca/dfw92yk/</t>
-        </is>
-      </c>
-      <c r="R9" s="2" t="inlineStr">
-        <is>
-          <t>San Antonio</t>
-        </is>
-      </c>
-      <c r="S9" s="2" t="inlineStr">
-        <is>
-          <t>0.66 mi</t>
-        </is>
-      </c>
-      <c r="T9" s="2" t="inlineStr">
-        <is>
-          <t>13 min</t>
-        </is>
-      </c>
-      <c r="U9" s="2" t="inlineStr">
-        <is>
-          <t>Another 2B/2B unit (B2J / Unit 412) was listed for Apr 23 and excluded from the eligible interpretation.</t>
-        </is>
-      </c>
-      <c r="V9" s="2" t="inlineStr">
-        <is>
-          <t>2026-03-17</t>
-        </is>
-      </c>
-      <c r="W9" s="2" t="inlineStr">
-        <is>
-          <t>Apartments.com live floor plan page</t>
-        </is>
-      </c>
-      <c r="X9" t="inlineStr">
-        <is>
-          <t>Estimated from listed distance at 20 min/mile because no explicit walking time was published</t>
-        </is>
-      </c>
-      <c r="Y9" t="inlineStr">
-        <is>
-          <t>In-unit washer/dryer</t>
-        </is>
-      </c>
-      <c r="Z9" t="inlineStr">
-        <is>
-          <t>Official UDR amenities page says in-home washer/dryer; Apartments.com and ApartmentHomeLiving also list in-unit Washer/Dryer.</t>
-        </is>
-      </c>
-      <c r="AA9" t="inlineStr">
-        <is>
-          <t>Official UDR pages say Verve has an in-home washer/dryer. ApartmentHomeLiving lists San Antonio Caltrain as the closest stop at 0.66 mi.</t>
-        </is>
-      </c>
-      <c r="AB9" t="inlineStr">
-        <is>
-          <t>https://www.udr.com/san-francisco-bay-area-apartments/mountain-view/verve/neighborhood/
-https://www.apartments.com/verve-mountain-view-ca/dfw92yk/
-https://www.apartmenthomeliving.com/apartment-finder/Verve-Mountain-View-CA-94040-3051240
-https://www.caltrain.com/station/sanantonio</t>
-        </is>
-      </c>
-      <c r="AC9" t="inlineStr">
-        <is>
-          <t>2026-03-18</t>
-        </is>
-      </c>
-      <c r="AD9" t="n">
-        <v>0.79</v>
-      </c>
-    </row>
-    <row r="10">
-      <c r="A10" s="2" t="inlineStr">
-        <is>
-          <t>The Shadows Apartments</t>
-        </is>
-      </c>
-      <c r="B10" s="2" t="inlineStr">
-        <is>
-          <t>Mountain View</t>
-        </is>
-      </c>
-      <c r="C10" s="2" t="inlineStr">
-        <is>
-          <t>ELIGIBLE</t>
-        </is>
-      </c>
-      <c r="D10" s="2" t="inlineStr">
-        <is>
-          <t>Now</t>
-        </is>
-      </c>
-      <c r="E10" s="2" t="inlineStr">
-        <is>
-          <t>2026-04-10</t>
-        </is>
-      </c>
-      <c r="F10" s="2" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="G10" s="2" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="H10" s="2" t="inlineStr">
-        <is>
-          <t>1,025</t>
-        </is>
-      </c>
-      <c r="I10" s="2" t="inlineStr">
-        <is>
-          <t>$4,595</t>
-        </is>
-      </c>
-      <c r="J10" s="2" t="inlineStr">
-        <is>
-          <t>Base rent</t>
-        </is>
-      </c>
-      <c r="K10" s="2" t="inlineStr">
-        <is>
-          <t>E floorplan</t>
-        </is>
-      </c>
-      <c r="L10" s="2" t="inlineStr">
-        <is>
-          <t>$1,000 off when you look and lease; water, sewer, and garbage included in rent</t>
-        </is>
-      </c>
-      <c r="M10" s="2" t="inlineStr">
-        <is>
-          <t>$800</t>
-        </is>
-      </c>
-      <c r="N10" s="2" t="inlineStr"/>
-      <c r="O10" s="2" t="inlineStr">
-        <is>
-          <t>4.0 (0 reviews)</t>
-        </is>
-      </c>
-      <c r="P10" s="2" t="inlineStr">
-        <is>
-          <t>https://www.shadowsapartments.com/</t>
-        </is>
-      </c>
-      <c r="Q10" s="3" t="inlineStr">
-        <is>
-          <t>https://www.apartments.com/the-shadows-apartments-mountain-view-ca/ysm3jjr/</t>
-        </is>
-      </c>
-      <c r="R10" s="2" t="inlineStr">
-        <is>
-          <t>Mountain View</t>
-        </is>
-      </c>
-      <c r="S10" s="2" t="inlineStr">
-        <is>
-          <t>1.0 mi</t>
-        </is>
-      </c>
-      <c r="T10" s="2" t="inlineStr">
-        <is>
-          <t>18 min</t>
-        </is>
-      </c>
-      <c r="U10" s="2" t="inlineStr">
-        <is>
-          <t>The 2B/2B floorplan was listed as available now without individual unit rows on Apartments.com.</t>
-        </is>
-      </c>
-      <c r="V10" s="2" t="inlineStr">
-        <is>
-          <t>2026-03-17</t>
-        </is>
-      </c>
-      <c r="W10" s="2" t="inlineStr">
-        <is>
-          <t>Apartments.com live floor plan page</t>
-        </is>
-      </c>
-      <c r="X10" t="inlineStr">
-        <is>
-          <t>Reported walking time from property transit listing</t>
-        </is>
-      </c>
-      <c r="Y10" t="inlineStr">
-        <is>
-          <t>In-unit washer/dryer</t>
-        </is>
-      </c>
-      <c r="Z10" t="inlineStr">
-        <is>
-          <t>Official site and Apartments.com both list in-unit washer/dryer; Apartments.com also lists shared laundry facilities in the community.</t>
-        </is>
-      </c>
-      <c r="AA10" t="inlineStr">
-        <is>
-          <t>Official site and Apartments.com identify The Shadows at 750 N Shoreline Blvd and both list in-unit washer/dryer. LoopNet shows Mountain View Caltrain at 1.0 mi / 18 min walk.</t>
-        </is>
-      </c>
-      <c r="AB10" t="inlineStr">
-        <is>
-          <t>https://www.shadowsapartments.com/
-https://www.apartments.com/the-shadows-apartments-mountain-view-ca/ysm3jjr/
-https://www.loopnet.com/property/750-n-shoreline-blvd-mountain-view-ca-94043/06085-15031038/
-https://www.caltrain.com/station/mountainview</t>
-        </is>
-      </c>
-      <c r="AC10" t="inlineStr">
-        <is>
-          <t>2026-03-18</t>
-        </is>
-      </c>
-      <c r="AD10" t="n">
-        <v>0.87</v>
-      </c>
-    </row>
-    <row r="11">
-      <c r="A11" s="2" t="inlineStr">
-        <is>
-          <t>MV Apartments</t>
-        </is>
-      </c>
-      <c r="B11" s="2" t="inlineStr">
-        <is>
-          <t>Mountain View</t>
-        </is>
-      </c>
-      <c r="C11" s="2" t="inlineStr">
-        <is>
-          <t>ELIGIBLE</t>
-        </is>
-      </c>
-      <c r="D11" s="2" t="inlineStr">
-        <is>
-          <t>Now</t>
-        </is>
-      </c>
-      <c r="E11" s="2" t="inlineStr">
-        <is>
-          <t>2026-04-10</t>
-        </is>
-      </c>
-      <c r="F11" s="2" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="G11" s="2" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="H11" s="2" t="inlineStr">
-        <is>
-          <t>1,013</t>
-        </is>
-      </c>
-      <c r="I11" s="2" t="inlineStr">
-        <is>
-          <t>$5,549</t>
-        </is>
-      </c>
-      <c r="J11" s="2" t="inlineStr">
-        <is>
-          <t>Base rent</t>
-        </is>
-      </c>
-      <c r="K11" s="2" t="inlineStr">
-        <is>
-          <t>Chestnut / Unit 528 now</t>
-        </is>
-      </c>
-      <c r="L11" s="2" t="inlineStr"/>
-      <c r="M11" s="2" t="inlineStr"/>
-      <c r="N11" s="2" t="inlineStr"/>
-      <c r="O11" s="2" t="inlineStr">
-        <is>
-          <t>4.8 (13 reviews)</t>
-        </is>
-      </c>
-      <c r="P11" s="2" t="inlineStr">
-        <is>
-          <t>https://www.mvapartments.com/</t>
-        </is>
-      </c>
-      <c r="Q11" s="3" t="inlineStr">
-        <is>
-          <t>https://www.apartments.com/mv-apartments-mountain-view-ca/tlm9sdb/</t>
-        </is>
-      </c>
-      <c r="R11" s="2" t="inlineStr">
-        <is>
-          <t>San Antonio</t>
-        </is>
-      </c>
-      <c r="S11" s="2" t="inlineStr">
-        <is>
-          <t>0.9 mi</t>
-        </is>
-      </c>
-      <c r="T11" s="2" t="inlineStr">
-        <is>
-          <t>16 min</t>
-        </is>
-      </c>
-      <c r="U11" s="2" t="inlineStr">
-        <is>
-          <t>A second Chestnut unit for Apr 14 was excluded from the eligible interpretation because it is after the cutoff.</t>
-        </is>
-      </c>
-      <c r="V11" s="2" t="inlineStr">
-        <is>
-          <t>2026-03-17</t>
-        </is>
-      </c>
-      <c r="W11" s="2" t="inlineStr">
-        <is>
-          <t>Apartments.com live floor plan page</t>
-        </is>
-      </c>
-      <c r="X11" t="inlineStr">
-        <is>
-          <t>Listing-stated walking time on Apartments.com</t>
-        </is>
-      </c>
-      <c r="Y11" t="inlineStr">
-        <is>
-          <t>In-unit washer/dryer</t>
-        </is>
-      </c>
-      <c r="Z11" t="inlineStr">
-        <is>
-          <t>Official site lists in-home laundry appliances and a full-size front-loading washer and dryer; Apartments.com also lists in-unit washers and dryers.</t>
-        </is>
-      </c>
-      <c r="AA11" t="inlineStr">
-        <is>
-          <t>Official MV Apartments site advertises in-home laundry appliances/full-size front-loading washer and dryer. Apartments.com lists San Antonio at 0.9 mi / 16 min walk.</t>
-        </is>
-      </c>
-      <c r="AB11" t="inlineStr">
-        <is>
-          <t>https://www.mvapartments.com/
-https://www.apartments.com/mv-apartments-mountain-view-ca/tlm9sdb/</t>
-        </is>
-      </c>
-      <c r="AC11" t="inlineStr">
-        <is>
-          <t>2026-03-18</t>
-        </is>
-      </c>
-      <c r="AD11" t="n">
-        <v>0.96</v>
-      </c>
-    </row>
-    <row r="12">
-      <c r="A12" s="2" t="inlineStr">
-        <is>
-          <t>Maplewood Apartments</t>
-        </is>
-      </c>
-      <c r="B12" s="2" t="inlineStr">
-        <is>
-          <t>Mountain View</t>
-        </is>
-      </c>
-      <c r="C12" s="2" t="inlineStr">
-        <is>
-          <t>ELIGIBLE</t>
-        </is>
-      </c>
-      <c r="D12" s="2" t="inlineStr">
-        <is>
-          <t>Now</t>
-        </is>
-      </c>
-      <c r="E12" s="2" t="inlineStr">
-        <is>
-          <t>2026-04-10</t>
-        </is>
-      </c>
-      <c r="F12" s="2" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="G12" s="2" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="H12" s="2" t="inlineStr">
-        <is>
-          <t>947</t>
-        </is>
-      </c>
-      <c r="I12" s="2" t="inlineStr">
-        <is>
-          <t>$3,700-$3,800</t>
-        </is>
-      </c>
-      <c r="J12" s="2" t="inlineStr">
-        <is>
-          <t>Base rent</t>
-        </is>
-      </c>
-      <c r="K12" s="2" t="inlineStr">
-        <is>
-          <t>Plan B1 / Unit 29 now; Unit 31 Apr 7</t>
-        </is>
-      </c>
-      <c r="L12" s="2" t="inlineStr">
-        <is>
-          <t>Up to 1 month on us</t>
-        </is>
-      </c>
-      <c r="M12" s="2" t="inlineStr">
-        <is>
-          <t>$600</t>
-        </is>
-      </c>
-      <c r="N12" s="2" t="inlineStr"/>
-      <c r="O12" s="2" t="inlineStr">
-        <is>
-          <t>4.0 (0 reviews)</t>
-        </is>
-      </c>
-      <c r="P12" s="2" t="inlineStr">
-        <is>
-          <t>https://livemaplewoodca.com/amenities.aspx</t>
-        </is>
-      </c>
-      <c r="Q12" s="3" t="inlineStr">
-        <is>
-          <t>https://www.apartments.com/maplewood-apartments-mountain-view-ca/0h511d1/</t>
-        </is>
-      </c>
-      <c r="R12" s="2" t="inlineStr">
-        <is>
-          <t>Mountain View</t>
-        </is>
-      </c>
-      <c r="S12" s="2" t="inlineStr">
-        <is>
-          <t>1.3 mi</t>
-        </is>
-      </c>
-      <c r="T12" s="2" t="inlineStr">
-        <is>
-          <t>26 min</t>
-        </is>
-      </c>
-      <c r="U12" s="2" t="inlineStr">
-        <is>
-          <t>Two 2B/2B units were live and both meet the early-April cutoff.</t>
-        </is>
-      </c>
-      <c r="V12" s="2" t="inlineStr">
-        <is>
-          <t>2026-03-17</t>
-        </is>
-      </c>
-      <c r="W12" s="2" t="inlineStr">
-        <is>
-          <t>Apartments.com live floor plan page</t>
-        </is>
-      </c>
-      <c r="X12" t="inlineStr">
-        <is>
-          <t>Estimated from the listed 1.3 mi distance at 20 min/mile; no published walking route was found</t>
-        </is>
-      </c>
-      <c r="Y12" t="inlineStr">
-        <is>
-          <t>In-unit washer/dryer</t>
-        </is>
-      </c>
-      <c r="Z12" t="inlineStr">
-        <is>
-          <t>Official site lists In-Home Washer &amp; Dryer; Apartments.com also says units have in-unit washers and dryers.</t>
-        </is>
-      </c>
-      <c r="AA12" t="inlineStr">
-        <is>
-          <t>Official Maplewood site shows 1885 California St and in-home washer/dryer. Apartments.com lists Mountain View Caltrain at 1.3 mi and San Antonio at 1.5 mi.</t>
-        </is>
-      </c>
-      <c r="AB12" t="inlineStr">
-        <is>
-          <t>https://livemaplewoodca.com/amenities.aspx
-https://www.apartments.com/maplewood-apartments-mountain-view-ca/0h511d1/
-https://www.apartmentfinder.com/California/Mountain-View-Apartments/Maplewood-Apartments</t>
-        </is>
-      </c>
-      <c r="AC12" t="inlineStr">
-        <is>
-          <t>2026-03-18</t>
-        </is>
-      </c>
-      <c r="AD12" t="n">
-        <v>0.68</v>
-      </c>
-    </row>
-    <row r="13">
-      <c r="A13" s="2" t="inlineStr">
-        <is>
-          <t>Hartwood</t>
-        </is>
-      </c>
-      <c r="B13" s="2" t="inlineStr">
-        <is>
-          <t>Sunnyvale</t>
-        </is>
-      </c>
-      <c r="C13" s="2" t="inlineStr">
-        <is>
-          <t>ELIGIBLE</t>
-        </is>
-      </c>
-      <c r="D13" s="2" t="inlineStr">
-        <is>
-          <t>Now</t>
-        </is>
-      </c>
-      <c r="E13" s="2" t="inlineStr">
-        <is>
-          <t>2026-04-10</t>
-        </is>
-      </c>
-      <c r="F13" s="2" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="G13" s="2" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="H13" s="2" t="inlineStr">
-        <is>
-          <t>1,223</t>
-        </is>
-      </c>
-      <c r="I13" s="2" t="inlineStr">
-        <is>
-          <t>$5,200-$5,515</t>
-        </is>
-      </c>
-      <c r="J13" s="2" t="inlineStr">
-        <is>
-          <t>Base rent</t>
-        </is>
-      </c>
-      <c r="K13" s="2" t="inlineStr">
-        <is>
-          <t>2 Bed/2 Bath-B5 / Unit 2109 now; Unit 2402 Apr 5; Unit 1307 Apr 7</t>
-        </is>
-      </c>
-      <c r="L13" s="2" t="inlineStr">
-        <is>
-          <t>Exceptional leasing specials available for a limited time</t>
-        </is>
-      </c>
-      <c r="M13" s="2" t="inlineStr"/>
-      <c r="N13" s="2" t="inlineStr"/>
-      <c r="O13" s="2" t="inlineStr">
-        <is>
-          <t>4.0 (0 reviews)</t>
-        </is>
-      </c>
-      <c r="P13" s="2" t="inlineStr">
-        <is>
-          <t>https://www.hartwoodsunnyvale.com/</t>
-        </is>
-      </c>
-      <c r="Q13" s="3" t="inlineStr">
-        <is>
-          <t>https://www.apartments.com/hartwood-sunnyvale-ca/nzqhytq/</t>
-        </is>
-      </c>
-      <c r="R13" s="2" t="inlineStr">
-        <is>
-          <t>Lawrence</t>
-        </is>
-      </c>
-      <c r="S13" s="2" t="inlineStr">
-        <is>
-          <t>0.1 mi</t>
-        </is>
-      </c>
-      <c r="T13" s="2" t="inlineStr">
-        <is>
-          <t>1 min</t>
-        </is>
-      </c>
-      <c r="U13" s="2" t="inlineStr">
-        <is>
-          <t>Other 2B/2B floorplans were listed but marked not available; B5 is the live qualifying option.</t>
-        </is>
-      </c>
-      <c r="V13" s="2" t="inlineStr">
-        <is>
-          <t>2026-03-17</t>
-        </is>
-      </c>
-      <c r="W13" s="2" t="inlineStr">
-        <is>
-          <t>Apartments.com live floor plan page</t>
-        </is>
-      </c>
-      <c r="X13" t="inlineStr">
-        <is>
-          <t>Listed walking time from Apartments.com</t>
-        </is>
-      </c>
-      <c r="Y13" t="inlineStr">
-        <is>
-          <t>In-unit washer/dryer</t>
-        </is>
-      </c>
-      <c r="Z13" t="inlineStr">
-        <is>
-          <t>Apartments.com lists Washer/Dryer in apartment features and says Hartwood has units with in-unit washers and dryers; the official site does not mention laundry.</t>
-        </is>
-      </c>
-      <c r="AA13" t="inlineStr">
-        <is>
-          <t>Hartwood’s official site says it is steps from Lawrence Station. Apartments.com lists Lawrence Caltrain at 0.1 mi / 1 min walk and confirms in-unit washer/dryer.</t>
-        </is>
-      </c>
-      <c r="AB13" t="inlineStr">
-        <is>
-          <t>https://www.hartwoodsunnyvale.com/neighborhood/
-https://www.apartments.com/hartwood-sunnyvale-ca/nzqhytq/</t>
-        </is>
-      </c>
-      <c r="AC13" t="inlineStr">
-        <is>
-          <t>2026-03-18</t>
-        </is>
-      </c>
-      <c r="AD13" t="n">
-        <v>0.88</v>
-      </c>
-    </row>
-    <row r="14">
-      <c r="A14" s="2" t="inlineStr">
-        <is>
-          <t>Savoy</t>
-        </is>
-      </c>
-      <c r="B14" s="2" t="inlineStr">
-        <is>
-          <t>Sunnyvale</t>
-        </is>
-      </c>
-      <c r="C14" s="2" t="inlineStr">
-        <is>
-          <t>ELIGIBLE</t>
-        </is>
-      </c>
-      <c r="D14" s="2" t="inlineStr">
-        <is>
-          <t>Now</t>
-        </is>
-      </c>
-      <c r="E14" s="2" t="inlineStr">
-        <is>
-          <t>2026-04-10</t>
-        </is>
-      </c>
-      <c r="F14" s="2" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="G14" s="2" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="H14" s="2" t="inlineStr">
-        <is>
-          <t>1,228-1,344</t>
-        </is>
-      </c>
-      <c r="I14" s="2" t="inlineStr">
-        <is>
-          <t>$4,946-$5,108</t>
-        </is>
-      </c>
-      <c r="J14" s="2" t="inlineStr">
-        <is>
-          <t>Total monthly price</t>
-        </is>
-      </c>
-      <c r="K14" s="2" t="inlineStr">
-        <is>
-          <t>B5.4 / Unit 1-415 now; B5 / Unit 2-550 Mar 24; B7 / Unit 2-321 Apr 8</t>
-        </is>
-      </c>
-      <c r="L14" s="2" t="inlineStr"/>
-      <c r="M14" s="2" t="inlineStr">
-        <is>
-          <t>$600</t>
-        </is>
-      </c>
-      <c r="N14" s="2" t="inlineStr"/>
-      <c r="O14" s="2" t="inlineStr">
-        <is>
-          <t>4.4 (98 reviews)</t>
-        </is>
-      </c>
-      <c r="P14" s="2" t="inlineStr">
-        <is>
-          <t>https://liveatsavoy.com/</t>
-        </is>
-      </c>
-      <c r="Q14" s="3" t="inlineStr">
-        <is>
-          <t>https://www.apartments.com/savoy-sunnyvale-ca/wz9c7ck/</t>
-        </is>
-      </c>
-      <c r="R14" s="2" t="inlineStr">
-        <is>
-          <t>Lawrence</t>
-        </is>
-      </c>
-      <c r="S14" s="2" t="inlineStr">
-        <is>
-          <t>0.6 mi</t>
-        </is>
-      </c>
-      <c r="T14" s="2" t="inlineStr">
-        <is>
-          <t>12 min</t>
-        </is>
-      </c>
-      <c r="U14" s="2" t="inlineStr">
-        <is>
-          <t>A B5 unit for Apr 23 and a B2 unit for Apr 29 were excluded from the eligible interpretation.</t>
-        </is>
-      </c>
-      <c r="V14" s="2" t="inlineStr">
-        <is>
-          <t>2026-03-17</t>
-        </is>
-      </c>
-      <c r="W14" s="2" t="inlineStr">
-        <is>
-          <t>Apartments.com live floor plan page</t>
-        </is>
-      </c>
-      <c r="X14" t="inlineStr">
-        <is>
-          <t>Listed walking time on Apartments.com</t>
-        </is>
-      </c>
-      <c r="Y14" t="inlineStr">
-        <is>
-          <t>In-unit washer/dryer</t>
-        </is>
-      </c>
-      <c r="Z14" t="inlineStr">
-        <is>
-          <t>Apartments.com lists Washer/Dryer under apartment features. The official site does not explicitly mention laundry, but nothing suggests shared-only laundry.</t>
-        </is>
-      </c>
-      <c r="AA14" t="inlineStr">
-        <is>
-          <t>Official site says Savoy is made accessible by Lawrence Station Caltrain and lists the property at 1120 Kifer Road. Apartments.com lists Lawrence at 0.6 mi / 12 min walk and shows washer/dryer in apartment features.</t>
-        </is>
-      </c>
-      <c r="AB14" t="inlineStr">
-        <is>
-          <t>https://liveatsavoy.com/
-https://liveatsavoy.com/amenities/
-https://www.apartments.com/savoy-sunnyvale-ca/wz9c7ck/</t>
-        </is>
-      </c>
-      <c r="AC14" t="inlineStr">
-        <is>
-          <t>2026-03-18</t>
-        </is>
-      </c>
-      <c r="AD14" t="n">
-        <v>0.88</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" s="2" t="inlineStr">
         <is>
-          <t>Encasa</t>
+          <t>Stanford Villa</t>
         </is>
       </c>
       <c r="B15" s="2" t="inlineStr">
         <is>
-          <t>Sunnyvale</t>
+          <t>Palo Alto</t>
         </is>
       </c>
       <c r="C15" s="2" t="inlineStr">
@@ -2529,7 +2542,7 @@
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>2026-03-24</t>
+          <t>Now</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
@@ -2549,60 +2562,64 @@
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>1,175</t>
+          <t>1,000-1,050</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>$4,855</t>
+          <t>$3,650-$4,170</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>Total monthly price</t>
+          <t>Base rent</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>2x2e / Unit 7423</t>
-        </is>
-      </c>
-      <c r="L15" s="2" t="inlineStr"/>
-      <c r="M15" s="2" t="inlineStr"/>
-      <c r="N15" s="2" t="inlineStr"/>
+          <t>Sequoia (Units 106 now, 140 Apr 1); Ponderosa (multiple units now)</t>
+        </is>
+      </c>
+      <c r="L15" s="2" t="n"/>
+      <c r="M15" s="2" t="inlineStr">
+        <is>
+          <t>$800</t>
+        </is>
+      </c>
+      <c r="N15" s="2" t="n"/>
       <c r="O15" s="2" t="inlineStr">
         <is>
-          <t>4.2 (24 reviews)</t>
-        </is>
-      </c>
-      <c r="P15" s="2" t="inlineStr">
-        <is>
-          <t>https://www.encasaliving.com/Contact.aspx</t>
+          <t>3.9 (5 reviews)</t>
+        </is>
+      </c>
+      <c r="P15" s="3" t="inlineStr">
+        <is>
+          <t>https://www.stanfordvilla.com/apartments/ca/palo-alto/amenities</t>
         </is>
       </c>
       <c r="Q15" s="3" t="inlineStr">
         <is>
-          <t>https://www.apartments.com/encasa-sunnyvale-ca/s1ktnb6/</t>
+          <t>https://www.apartments.com/stanford-villa-palo-alto-ca/5ezwzbq/</t>
         </is>
       </c>
       <c r="R15" s="2" t="inlineStr">
         <is>
-          <t>Lawrence</t>
+          <t>California Ave</t>
         </is>
       </c>
       <c r="S15" s="2" t="inlineStr">
         <is>
-          <t>3.0 mi</t>
+          <t>1.5 mi</t>
         </is>
       </c>
       <c r="T15" s="2" t="inlineStr">
         <is>
-          <t>60 min</t>
+          <t>30 min</t>
         </is>
       </c>
       <c r="U15" s="2" t="inlineStr">
         <is>
-          <t>Only one live 2B/2B unit met the cutoff; the rest of the 2B/2B plans were not available.</t>
+          <t>Two 2B/2B floorplans were live: Sequoia 1,000 sq ft and Ponderosa 1,050 sq ft.</t>
         </is>
       </c>
       <c r="V15" s="2" t="inlineStr">
@@ -2617,28 +2634,29 @@
       </c>
       <c r="X15" t="inlineStr">
         <is>
-          <t>Estimated from listed walking distance at 20 min/mile</t>
+          <t>Estimated from walking distance at 20 min/mile</t>
         </is>
       </c>
       <c r="Y15" t="inlineStr">
         <is>
-          <t>In-unit washer/dryer</t>
+          <t>No in-unit washer/dryer</t>
         </is>
       </c>
       <c r="Z15" t="inlineStr">
         <is>
-          <t>Official site lists In Unit Washer &amp; Dryer - Stackable; Apartments.com also lists in-unit washer/dryer.</t>
+          <t>No in-unit laundry; official site lists on-site laundry facilities (card-operated), and Apartments.com says on-site laundry is shared resident use.</t>
         </is>
       </c>
       <c r="AA15" t="inlineStr">
         <is>
-          <t>Encasa’s official site lists an in-unit stackable washer/dryer. Apartments.com shows Lawrence as the closest Caltrain stop at 3.0 mi, so the walk time was estimated.</t>
+          <t>Official sources confirm on-site shared laundry rather than in-unit laundry. California Ave is the closest Caltrain stop; LoopNet showed 1.5 mi and Apartments.com showed 1.8 mi, so 1.5 mi was used.</t>
         </is>
       </c>
       <c r="AB15" t="inlineStr">
         <is>
-          <t>https://www.encasaliving.com/Contact.aspx
-https://www.apartments.com/es/encasa-sunnyvale-ca/s1ktnb6/</t>
+          <t>https://rde.stanford.edu/studenthousing/stanford-villa-apartments
+https://www.apartments.com/stanford-villa-palo-alto-ca/5ezwzbq/
+https://www.loopnet.com/property/3375-alma-st-palo-alto-ca-94306/06085-13228075/</t>
         </is>
       </c>
       <c r="AC15" t="inlineStr">
@@ -2647,278 +2665,847 @@
         </is>
       </c>
       <c r="AD15" t="n">
-        <v>0.84</v>
+        <v>0.89</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" s="2" t="inlineStr">
         <is>
+          <t>Encasa</t>
+        </is>
+      </c>
+      <c r="B16" s="2" t="inlineStr">
+        <is>
+          <t>Sunnyvale</t>
+        </is>
+      </c>
+      <c r="C16" s="2" t="inlineStr">
+        <is>
+          <t>ELIGIBLE</t>
+        </is>
+      </c>
+      <c r="D16" s="2" t="inlineStr">
+        <is>
+          <t>2026-03-24</t>
+        </is>
+      </c>
+      <c r="E16" s="2" t="inlineStr">
+        <is>
+          <t>2026-04-10</t>
+        </is>
+      </c>
+      <c r="F16" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="G16" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="H16" s="2" t="inlineStr">
+        <is>
+          <t>1,175</t>
+        </is>
+      </c>
+      <c r="I16" s="2" t="inlineStr">
+        <is>
+          <t>$4,855</t>
+        </is>
+      </c>
+      <c r="J16" s="2" t="inlineStr">
+        <is>
+          <t>Total monthly price</t>
+        </is>
+      </c>
+      <c r="K16" s="2" t="inlineStr">
+        <is>
+          <t>2x2e / Unit 7423</t>
+        </is>
+      </c>
+      <c r="L16" s="2" t="n"/>
+      <c r="M16" s="2" t="n"/>
+      <c r="N16" s="2" t="n"/>
+      <c r="O16" s="2" t="inlineStr">
+        <is>
+          <t>4.2 (24 reviews)</t>
+        </is>
+      </c>
+      <c r="P16" s="3" t="inlineStr">
+        <is>
+          <t>https://www.encasaliving.com/Contact.aspx</t>
+        </is>
+      </c>
+      <c r="Q16" s="3" t="inlineStr">
+        <is>
+          <t>https://www.apartments.com/encasa-sunnyvale-ca/s1ktnb6/</t>
+        </is>
+      </c>
+      <c r="R16" s="2" t="inlineStr">
+        <is>
+          <t>Lawrence</t>
+        </is>
+      </c>
+      <c r="S16" s="2" t="inlineStr">
+        <is>
+          <t>3.0 mi</t>
+        </is>
+      </c>
+      <c r="T16" s="2" t="inlineStr">
+        <is>
+          <t>60 min</t>
+        </is>
+      </c>
+      <c r="U16" s="2" t="inlineStr">
+        <is>
+          <t>Only one live 2B/2B unit met the cutoff; the rest of the 2B/2B plans were not available.</t>
+        </is>
+      </c>
+      <c r="V16" s="2" t="inlineStr">
+        <is>
+          <t>2026-03-17</t>
+        </is>
+      </c>
+      <c r="W16" s="2" t="inlineStr">
+        <is>
+          <t>Apartments.com live floor plan page</t>
+        </is>
+      </c>
+      <c r="X16" t="inlineStr">
+        <is>
+          <t>Estimated from listed walking distance at 20 min/mile</t>
+        </is>
+      </c>
+      <c r="Y16" t="inlineStr">
+        <is>
+          <t>In-unit washer/dryer</t>
+        </is>
+      </c>
+      <c r="Z16" t="inlineStr">
+        <is>
+          <t>Official site lists In Unit Washer &amp; Dryer - Stackable; Apartments.com also lists in-unit washer/dryer.</t>
+        </is>
+      </c>
+      <c r="AA16" t="inlineStr">
+        <is>
+          <t>Encasa’s official site lists an in-unit stackable washer/dryer. Apartments.com shows Lawrence as the closest Caltrain stop at 3.0 mi, so the walk time was estimated.</t>
+        </is>
+      </c>
+      <c r="AB16" t="inlineStr">
+        <is>
+          <t>https://www.encasaliving.com/Contact.aspx
+https://www.apartments.com/es/encasa-sunnyvale-ca/s1ktnb6/</t>
+        </is>
+      </c>
+      <c r="AC16" t="inlineStr">
+        <is>
+          <t>2026-03-18</t>
+        </is>
+      </c>
+      <c r="AD16" t="n">
+        <v>0.84</v>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="2" t="inlineStr">
+        <is>
+          <t>Hartwood</t>
+        </is>
+      </c>
+      <c r="B17" s="2" t="inlineStr">
+        <is>
+          <t>Sunnyvale</t>
+        </is>
+      </c>
+      <c r="C17" s="2" t="inlineStr">
+        <is>
+          <t>ELIGIBLE</t>
+        </is>
+      </c>
+      <c r="D17" s="2" t="inlineStr">
+        <is>
+          <t>Now</t>
+        </is>
+      </c>
+      <c r="E17" s="2" t="inlineStr">
+        <is>
+          <t>2026-04-10</t>
+        </is>
+      </c>
+      <c r="F17" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="G17" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="H17" s="2" t="inlineStr">
+        <is>
+          <t>1,223</t>
+        </is>
+      </c>
+      <c r="I17" s="2" t="inlineStr">
+        <is>
+          <t>$5,200-$5,515</t>
+        </is>
+      </c>
+      <c r="J17" s="2" t="inlineStr">
+        <is>
+          <t>Base rent</t>
+        </is>
+      </c>
+      <c r="K17" s="2" t="inlineStr">
+        <is>
+          <t>2 Bed/2 Bath-B5 / Unit 2109 now; Unit 2402 Apr 5; Unit 1307 Apr 7</t>
+        </is>
+      </c>
+      <c r="L17" s="2" t="inlineStr">
+        <is>
+          <t>Exceptional leasing specials available for a limited time</t>
+        </is>
+      </c>
+      <c r="M17" s="2" t="n"/>
+      <c r="N17" s="2" t="n"/>
+      <c r="O17" s="2" t="inlineStr">
+        <is>
+          <t>4.0 (0 reviews)</t>
+        </is>
+      </c>
+      <c r="P17" s="3" t="inlineStr">
+        <is>
+          <t>https://www.hartwoodsunnyvale.com/</t>
+        </is>
+      </c>
+      <c r="Q17" s="3" t="inlineStr">
+        <is>
+          <t>https://www.apartments.com/hartwood-sunnyvale-ca/nzqhytq/</t>
+        </is>
+      </c>
+      <c r="R17" s="2" t="inlineStr">
+        <is>
+          <t>Lawrence</t>
+        </is>
+      </c>
+      <c r="S17" s="2" t="inlineStr">
+        <is>
+          <t>0.1 mi</t>
+        </is>
+      </c>
+      <c r="T17" s="2" t="inlineStr">
+        <is>
+          <t>1 min</t>
+        </is>
+      </c>
+      <c r="U17" s="2" t="inlineStr">
+        <is>
+          <t>Other 2B/2B floorplans were listed but marked not available; B5 is the live qualifying option.</t>
+        </is>
+      </c>
+      <c r="V17" s="2" t="inlineStr">
+        <is>
+          <t>2026-03-17</t>
+        </is>
+      </c>
+      <c r="W17" s="2" t="inlineStr">
+        <is>
+          <t>Apartments.com live floor plan page</t>
+        </is>
+      </c>
+      <c r="X17" t="inlineStr">
+        <is>
+          <t>Listed walking time from Apartments.com</t>
+        </is>
+      </c>
+      <c r="Y17" t="inlineStr">
+        <is>
+          <t>In-unit washer/dryer</t>
+        </is>
+      </c>
+      <c r="Z17" t="inlineStr">
+        <is>
+          <t>Apartments.com lists Washer/Dryer in apartment features and says Hartwood has units with in-unit washers and dryers; the official site does not mention laundry.</t>
+        </is>
+      </c>
+      <c r="AA17" t="inlineStr">
+        <is>
+          <t>Hartwood’s official site says it is steps from Lawrence Station. Apartments.com lists Lawrence Caltrain at 0.1 mi / 1 min walk and confirms in-unit washer/dryer.</t>
+        </is>
+      </c>
+      <c r="AB17" t="inlineStr">
+        <is>
+          <t>https://www.hartwoodsunnyvale.com/neighborhood/
+https://www.apartments.com/hartwood-sunnyvale-ca/nzqhytq/</t>
+        </is>
+      </c>
+      <c r="AC17" t="inlineStr">
+        <is>
+          <t>2026-03-18</t>
+        </is>
+      </c>
+      <c r="AD17" t="n">
+        <v>0.88</v>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="2" t="inlineStr">
+        <is>
+          <t>Heritage Park</t>
+        </is>
+      </c>
+      <c r="B18" s="2" t="inlineStr">
+        <is>
+          <t>Sunnyvale</t>
+        </is>
+      </c>
+      <c r="C18" s="2" t="inlineStr">
+        <is>
+          <t>ELIGIBLE</t>
+        </is>
+      </c>
+      <c r="D18" s="2" t="inlineStr">
+        <is>
+          <t>Now</t>
+        </is>
+      </c>
+      <c r="E18" s="2" t="inlineStr">
+        <is>
+          <t>2026-04-10</t>
+        </is>
+      </c>
+      <c r="F18" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="G18" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="H18" s="2" t="inlineStr">
+        <is>
+          <t>920</t>
+        </is>
+      </c>
+      <c r="I18" s="2" t="inlineStr">
+        <is>
+          <t>$3,280-$4,460</t>
+        </is>
+      </c>
+      <c r="J18" s="2" t="inlineStr">
+        <is>
+          <t>Base rent</t>
+        </is>
+      </c>
+      <c r="K18" s="2" t="inlineStr">
+        <is>
+          <t>2x2 / Units 309E now, 1406E now, 1107W now, 409E Apr 8</t>
+        </is>
+      </c>
+      <c r="L18" s="2" t="n"/>
+      <c r="M18" s="2" t="n"/>
+      <c r="N18" s="2" t="inlineStr">
+        <is>
+          <t>1-12 months</t>
+        </is>
+      </c>
+      <c r="O18" s="2" t="inlineStr">
+        <is>
+          <t>4.5 (11 reviews)</t>
+        </is>
+      </c>
+      <c r="P18" s="3" t="inlineStr">
+        <is>
+          <t>https://www.liveatheritageparkapts.com/amenities</t>
+        </is>
+      </c>
+      <c r="Q18" s="3" t="inlineStr">
+        <is>
+          <t>https://www.apartments.com/heritage-park-sunnyvale-ca/h2ctem3/</t>
+        </is>
+      </c>
+      <c r="R18" s="2" t="inlineStr">
+        <is>
+          <t>Sunnyvale</t>
+        </is>
+      </c>
+      <c r="S18" s="2" t="inlineStr">
+        <is>
+          <t>0.7 mi</t>
+        </is>
+      </c>
+      <c r="T18" s="2" t="inlineStr">
+        <is>
+          <t>13 min</t>
+        </is>
+      </c>
+      <c r="U18" s="2" t="inlineStr">
+        <is>
+          <t>A 2x2 unit for Apr 12 was excluded from the eligible interpretation.</t>
+        </is>
+      </c>
+      <c r="V18" s="2" t="inlineStr">
+        <is>
+          <t>2026-03-17</t>
+        </is>
+      </c>
+      <c r="W18" s="2" t="inlineStr">
+        <is>
+          <t>Apartments.com live floor plan page</t>
+        </is>
+      </c>
+      <c r="X18" t="inlineStr">
+        <is>
+          <t>Listed walking time/distance from Apartments.com commuter rail listing</t>
+        </is>
+      </c>
+      <c r="Y18" t="inlineStr">
+        <is>
+          <t>No in-unit washer/dryer</t>
+        </is>
+      </c>
+      <c r="Z18" t="inlineStr">
+        <is>
+          <t>Official amenities list Laundry Facilities as a community amenity, and Apartments.com FAQ says Heritage Park does not provide in-unit laundry and has on-site laundry facilities for shared resident use.</t>
+        </is>
+      </c>
+      <c r="AA18" t="inlineStr">
+        <is>
+          <t>Official site confirms proximity to Sunnyvale Caltrain and lists community laundry facilities. Apartments.com specifies a 13-minute, 0.7-mile walk and states there is no in-unit laundry.</t>
+        </is>
+      </c>
+      <c r="AB18" t="inlineStr">
+        <is>
+          <t>https://www.liveatheritageparkapts.com/amenities
+https://www.apartments.com/heritage-park-sunnyvale-ca/h2ctem3/</t>
+        </is>
+      </c>
+      <c r="AC18" t="inlineStr">
+        <is>
+          <t>2026-03-18</t>
+        </is>
+      </c>
+      <c r="AD18" t="n">
+        <v>0.95</v>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" s="2" t="inlineStr">
+        <is>
+          <t>Ironworks</t>
+        </is>
+      </c>
+      <c r="B19" s="2" t="inlineStr">
+        <is>
+          <t>Sunnyvale</t>
+        </is>
+      </c>
+      <c r="C19" s="2" t="inlineStr">
+        <is>
+          <t>ELIGIBLE</t>
+        </is>
+      </c>
+      <c r="D19" s="2" t="inlineStr">
+        <is>
+          <t>Now</t>
+        </is>
+      </c>
+      <c r="E19" s="2" t="inlineStr">
+        <is>
+          <t>2026-04-10</t>
+        </is>
+      </c>
+      <c r="F19" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="G19" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="H19" s="2" t="inlineStr">
+        <is>
+          <t>1,087-1,178</t>
+        </is>
+      </c>
+      <c r="I19" s="2" t="inlineStr">
+        <is>
+          <t>$4,801+</t>
+        </is>
+      </c>
+      <c r="J19" s="2" t="inlineStr">
+        <is>
+          <t>Base rent</t>
+        </is>
+      </c>
+      <c r="K19" s="2" t="inlineStr">
+        <is>
+          <t>2A (Units 161, 261, 348 now); 2D (Unit 372 Apr 4)</t>
+        </is>
+      </c>
+      <c r="L19" s="2" t="inlineStr">
+        <is>
+          <t>Up to one month free</t>
+        </is>
+      </c>
+      <c r="M19" s="2" t="n"/>
+      <c r="N19" s="2" t="n"/>
+      <c r="O19" s="2" t="inlineStr">
+        <is>
+          <t>4.8 (4 reviews)</t>
+        </is>
+      </c>
+      <c r="P19" s="3" t="inlineStr">
+        <is>
+          <t>https://prometheusapartments.com/ca/sunnyvale-apartments/ironworks</t>
+        </is>
+      </c>
+      <c r="Q19" s="3" t="inlineStr">
+        <is>
+          <t>https://www.apartments.com/ironworks-sunnyvale-ca/pqr7qwv/</t>
+        </is>
+      </c>
+      <c r="R19" s="2" t="inlineStr">
+        <is>
+          <t>Sunnyvale</t>
+        </is>
+      </c>
+      <c r="S19" s="2" t="inlineStr">
+        <is>
+          <t>0.4 mi</t>
+        </is>
+      </c>
+      <c r="T19" s="2" t="inlineStr">
+        <is>
+          <t>8 min</t>
+        </is>
+      </c>
+      <c r="U19" s="2" t="inlineStr">
+        <is>
+          <t>Ironworks adds another large, transit-friendly downtown Sunnyvale option with current 2B/2B inventory and strong resident feedback.</t>
+        </is>
+      </c>
+      <c r="V19" s="2" t="inlineStr">
+        <is>
+          <t>2026-03-18</t>
+        </is>
+      </c>
+      <c r="W19" s="2" t="inlineStr">
+        <is>
+          <t>Apartments.com exact property page plus Prometheus official page</t>
+        </is>
+      </c>
+      <c r="X19" t="inlineStr">
+        <is>
+          <t>Listed walking time/distance from Apartments.com transportation section</t>
+        </is>
+      </c>
+      <c r="Y19" t="inlineStr">
+        <is>
+          <t>In-unit washer/dryer</t>
+        </is>
+      </c>
+      <c r="Z19" t="inlineStr">
+        <is>
+          <t>Apartments.com lists Washer/Dryer in unit features for Ironworks.</t>
+        </is>
+      </c>
+      <c r="AA19" t="inlineStr">
+        <is>
+          <t>Apartments.com shows Sunnyvale Caltrain at a 0.4-mile, 8-minute walk and confirms in-unit washer/dryer. The Sunnyvale station transit listings also show Ironworks with live 2-bedroom inventory.</t>
+        </is>
+      </c>
+      <c r="AB19" t="inlineStr">
+        <is>
+          <t>https://prometheusapartments.com/ca/sunnyvale-apartments/ironworks
+https://www.apartments.com/ironworks-sunnyvale-ca/pqr7qwv/
+https://www.apartments.com/transit/ca/sunnyvale/sunnyvale-caltrain-station-southbound/tptz9t8/</t>
+        </is>
+      </c>
+      <c r="AC19" t="inlineStr">
+        <is>
+          <t>2026-03-18</t>
+        </is>
+      </c>
+      <c r="AD19" t="n">
+        <v>0.95</v>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" s="2" t="inlineStr">
+        <is>
           <t>Naya</t>
         </is>
       </c>
-      <c r="B16" s="2" t="inlineStr">
+      <c r="B20" s="2" t="inlineStr">
         <is>
           <t>Sunnyvale</t>
         </is>
       </c>
-      <c r="C16" s="2" t="inlineStr">
+      <c r="C20" s="2" t="inlineStr">
         <is>
           <t>ELIGIBLE</t>
         </is>
       </c>
-      <c r="D16" s="2" t="inlineStr">
+      <c r="D20" s="2" t="inlineStr">
         <is>
           <t>2026-03-19</t>
         </is>
       </c>
-      <c r="E16" s="2" t="inlineStr">
+      <c r="E20" s="2" t="inlineStr">
         <is>
           <t>2026-04-10</t>
         </is>
       </c>
-      <c r="F16" s="2" t="inlineStr">
+      <c r="F20" s="2" t="inlineStr">
         <is>
           <t>2</t>
         </is>
       </c>
-      <c r="G16" s="2" t="inlineStr">
+      <c r="G20" s="2" t="inlineStr">
         <is>
           <t>2</t>
         </is>
       </c>
-      <c r="H16" s="2" t="inlineStr">
+      <c r="H20" s="2" t="inlineStr">
         <is>
           <t>1,013</t>
         </is>
       </c>
-      <c r="I16" s="2" t="inlineStr">
+      <c r="I20" s="2" t="inlineStr">
         <is>
           <t>$4,789</t>
         </is>
       </c>
-      <c r="J16" s="2" t="inlineStr">
+      <c r="J20" s="2" t="inlineStr">
         <is>
           <t>Total monthly price</t>
         </is>
       </c>
-      <c r="K16" s="2" t="inlineStr">
+      <c r="K20" s="2" t="inlineStr">
         <is>
           <t>Floor Plan C / Unit 303</t>
         </is>
       </c>
-      <c r="L16" s="2" t="inlineStr"/>
-      <c r="M16" s="2" t="inlineStr"/>
-      <c r="N16" s="2" t="inlineStr"/>
-      <c r="O16" s="2" t="inlineStr">
+      <c r="L20" s="2" t="n"/>
+      <c r="M20" s="2" t="n"/>
+      <c r="N20" s="2" t="n"/>
+      <c r="O20" s="2" t="inlineStr">
         <is>
           <t>4.8 (25 reviews)</t>
         </is>
       </c>
-      <c r="P16" s="2" t="inlineStr">
+      <c r="P20" s="3" t="inlineStr">
         <is>
           <t>https://www.greystar.com/naya-sunnyvale-ca/p_17093</t>
         </is>
       </c>
-      <c r="Q16" s="3" t="inlineStr">
+      <c r="Q20" s="3" t="inlineStr">
         <is>
           <t>https://www.apartments.com/naya-sunnyvale-ca/prdh34v/</t>
         </is>
       </c>
-      <c r="R16" s="2" t="inlineStr">
+      <c r="R20" s="2" t="inlineStr">
         <is>
           <t>Sunnyvale</t>
         </is>
       </c>
-      <c r="S16" s="2" t="inlineStr">
+      <c r="S20" s="2" t="inlineStr">
         <is>
           <t>1.2 mi</t>
         </is>
       </c>
-      <c r="T16" s="2" t="inlineStr">
+      <c r="T20" s="2" t="inlineStr">
         <is>
           <t>24 min</t>
         </is>
       </c>
-      <c r="U16" s="2" t="inlineStr">
+      <c r="U20" s="2" t="inlineStr">
         <is>
           <t>A second 2B/2B plan (Floor Plan E / Unit 302) was listed for Apr 12 and excluded from the eligible interpretation.</t>
         </is>
       </c>
-      <c r="V16" s="2" t="inlineStr">
+      <c r="V20" s="2" t="inlineStr">
         <is>
           <t>2026-03-17</t>
         </is>
       </c>
-      <c r="W16" s="2" t="inlineStr">
+      <c r="W20" s="2" t="inlineStr">
         <is>
           <t>Apartments.com live floor plan page</t>
         </is>
       </c>
-      <c r="X16" t="inlineStr">
+      <c r="X20" t="inlineStr">
         <is>
           <t>Estimated from Walk Score rail-line distance at 20 min/mile; no explicit walking time was found on listing sites</t>
         </is>
       </c>
-      <c r="Y16" t="inlineStr">
+      <c r="Y20" t="inlineStr">
         <is>
           <t>Likely in-unit washer/dryer (conflicting sources)</t>
         </is>
       </c>
-      <c r="Z16" t="inlineStr">
+      <c r="Z20" t="inlineStr">
         <is>
           <t>Greystar’s official page lists Washer/Dryer and Full Size Washer/Dryer, but Apartments.com FAQ contradicts that with a no in-unit/shared-laundry statement. Official site indicates in-unit laundry; third-party listing is inconsistent.</t>
         </is>
       </c>
-      <c r="AA16" t="inlineStr">
+      <c r="AA20" t="inlineStr">
         <is>
           <t>Official Naya listing places the property at 1095 W El Camino Real and shows washer/dryer. Walk Score for that address shows rail lines 1.2 mi away, which was used as the best walk-distance proxy.</t>
         </is>
       </c>
-      <c r="AB16" t="inlineStr">
+      <c r="AB20" t="inlineStr">
         <is>
           <t>https://www.greystar.com/naya-sunnyvale-ca/p_17093
 https://www.apartments.com/naya-sunnyvale-ca/prdh34v/
 https://www.walkscore.com/score/naya-two-br-sunnyvale</t>
         </is>
       </c>
-      <c r="AC16" t="inlineStr">
+      <c r="AC20" t="inlineStr">
         <is>
           <t>2026-03-18</t>
         </is>
       </c>
-      <c r="AD16" t="n">
+      <c r="AD20" t="n">
         <v>0.6899999999999999</v>
       </c>
     </row>
-    <row r="17">
-      <c r="A17" s="2" t="inlineStr">
+    <row r="21">
+      <c r="A21" s="2" t="inlineStr">
         <is>
           <t>Redwood Place Apartment Homes</t>
         </is>
       </c>
-      <c r="B17" s="2" t="inlineStr">
+      <c r="B21" s="2" t="inlineStr">
         <is>
           <t>Sunnyvale</t>
         </is>
       </c>
-      <c r="C17" s="2" t="inlineStr">
+      <c r="C21" s="2" t="inlineStr">
         <is>
           <t>ELIGIBLE</t>
         </is>
       </c>
-      <c r="D17" s="2" t="inlineStr">
+      <c r="D21" s="2" t="inlineStr">
         <is>
           <t>2026-03-25</t>
         </is>
       </c>
-      <c r="E17" s="2" t="inlineStr">
+      <c r="E21" s="2" t="inlineStr">
         <is>
           <t>2026-04-10</t>
         </is>
       </c>
-      <c r="F17" s="2" t="inlineStr">
+      <c r="F21" s="2" t="inlineStr">
         <is>
           <t>2</t>
         </is>
       </c>
-      <c r="G17" s="2" t="inlineStr">
+      <c r="G21" s="2" t="inlineStr">
         <is>
           <t>2</t>
         </is>
       </c>
-      <c r="H17" s="2" t="inlineStr">
+      <c r="H21" s="2" t="inlineStr">
         <is>
           <t>944-1,214</t>
         </is>
       </c>
-      <c r="I17" s="2" t="inlineStr">
+      <c r="I21" s="2" t="inlineStr">
         <is>
           <t>$4,660-$6,425</t>
         </is>
       </c>
-      <c r="J17" s="2" t="inlineStr">
+      <c r="J21" s="2" t="inlineStr">
         <is>
           <t>Base rent</t>
         </is>
       </c>
-      <c r="K17" s="2" t="inlineStr">
+      <c r="K21" s="2" t="inlineStr">
         <is>
           <t>Plan 15 / Unit 124 Apr 9; Plan 40 / Unit 1131 Apr 5; Plan 48 / Unit 0960 Apr 9</t>
         </is>
       </c>
-      <c r="L17" s="2" t="inlineStr"/>
-      <c r="M17" s="2" t="inlineStr">
+      <c r="L21" s="2" t="n"/>
+      <c r="M21" s="2" t="inlineStr">
         <is>
           <t>Varies by floorplan</t>
         </is>
       </c>
-      <c r="N17" s="2" t="inlineStr"/>
-      <c r="O17" s="2" t="inlineStr">
+      <c r="N21" s="2" t="n"/>
+      <c r="O21" s="2" t="inlineStr">
         <is>
           <t>4.7 (4 reviews)</t>
         </is>
       </c>
-      <c r="P17" s="2" t="inlineStr">
+      <c r="P21" s="3" t="inlineStr">
         <is>
           <t>https://www.irvinecompanyapartments.com/locations/northern-california/sunnyvale/redwood-place.html</t>
         </is>
       </c>
-      <c r="Q17" s="3" t="inlineStr">
+      <c r="Q21" s="3" t="inlineStr">
         <is>
           <t>https://www.apartments.com/redwood-place-apartment-homes-sunnyvale-ca/f5mc4nv/</t>
         </is>
       </c>
-      <c r="R17" s="2" t="inlineStr">
+      <c r="R21" s="2" t="inlineStr">
         <is>
           <t>Lawrence</t>
         </is>
       </c>
-      <c r="S17" s="2" t="inlineStr">
+      <c r="S21" s="2" t="inlineStr">
         <is>
           <t>1.33 mi</t>
         </is>
       </c>
-      <c r="T17" s="2" t="inlineStr">
+      <c r="T21" s="2" t="inlineStr">
         <is>
           <t>28 min</t>
         </is>
       </c>
-      <c r="U17" s="2" t="inlineStr">
+      <c r="U21" s="2" t="inlineStr">
         <is>
           <t>Plan 15 / Unit 300 for Apr 24 was excluded from the eligible interpretation.</t>
         </is>
       </c>
-      <c r="V17" s="2" t="inlineStr">
+      <c r="V21" s="2" t="inlineStr">
         <is>
           <t>2026-03-17</t>
         </is>
       </c>
-      <c r="W17" s="2" t="inlineStr">
+      <c r="W21" s="2" t="inlineStr">
         <is>
           <t>Apartments.com live floor plan page</t>
         </is>
       </c>
-      <c r="X17" t="inlineStr">
+      <c r="X21" t="inlineStr">
         <is>
           <t>Direct walking result from Moovit for the same address, not an estimate</t>
         </is>
       </c>
-      <c r="Y17" t="inlineStr">
+      <c r="Y21" t="inlineStr">
         <is>
           <t>In-unit washer/dryer</t>
         </is>
       </c>
-      <c r="Z17" t="inlineStr">
+      <c r="Z21" t="inlineStr">
         <is>
           <t>Official site lists in-home washer &amp; dryer; Apartments.com also lists Washer/Dryer.</t>
         </is>
       </c>
-      <c r="AA17" t="inlineStr">
+      <c r="AA21" t="inlineStr">
         <is>
           <t>Official Irvine Company pages confirm the address and in-home washer/dryer. Moovit lists Lawrence as the nearest train station at about 1.33 mi / 28 min walk.</t>
         </is>
       </c>
-      <c r="AB17" t="inlineStr">
+      <c r="AB21" t="inlineStr">
         <is>
           <t>https://www.irvinecompanyapartments.com/locations/northern-california/sunnyvale/redwood-place.html
 https://www.irvinecompanyapartments.com/locations/northern-california/sunnyvale/redwood-place/features.html
@@ -2926,144 +3513,574 @@
 https://moovitapp.com/index/en/public_transit-Santa_Clara_Square-SF_Bay_Area_CA-site_268971200-22</t>
         </is>
       </c>
-      <c r="AC17" t="inlineStr">
+      <c r="AC21" t="inlineStr">
         <is>
           <t>2026-03-18</t>
         </is>
       </c>
-      <c r="AD17" t="n">
+      <c r="AD21" t="n">
         <v>0.89</v>
       </c>
     </row>
-    <row r="18">
-      <c r="A18" s="2" t="inlineStr">
+    <row r="22">
+      <c r="A22" s="2" t="inlineStr">
+        <is>
+          <t>Savoy</t>
+        </is>
+      </c>
+      <c r="B22" s="2" t="inlineStr">
+        <is>
+          <t>Sunnyvale</t>
+        </is>
+      </c>
+      <c r="C22" s="2" t="inlineStr">
+        <is>
+          <t>ELIGIBLE</t>
+        </is>
+      </c>
+      <c r="D22" s="2" t="inlineStr">
+        <is>
+          <t>Now</t>
+        </is>
+      </c>
+      <c r="E22" s="2" t="inlineStr">
+        <is>
+          <t>2026-04-10</t>
+        </is>
+      </c>
+      <c r="F22" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="G22" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="H22" s="2" t="inlineStr">
+        <is>
+          <t>1,228-1,344</t>
+        </is>
+      </c>
+      <c r="I22" s="2" t="inlineStr">
+        <is>
+          <t>$4,946-$5,108</t>
+        </is>
+      </c>
+      <c r="J22" s="2" t="inlineStr">
+        <is>
+          <t>Total monthly price</t>
+        </is>
+      </c>
+      <c r="K22" s="2" t="inlineStr">
+        <is>
+          <t>B5.4 / Unit 1-415 now; B5 / Unit 2-550 Mar 24; B7 / Unit 2-321 Apr 8</t>
+        </is>
+      </c>
+      <c r="L22" s="2" t="n"/>
+      <c r="M22" s="2" t="inlineStr">
+        <is>
+          <t>$600</t>
+        </is>
+      </c>
+      <c r="N22" s="2" t="n"/>
+      <c r="O22" s="2" t="inlineStr">
+        <is>
+          <t>4.4 (98 reviews)</t>
+        </is>
+      </c>
+      <c r="P22" s="3" t="inlineStr">
+        <is>
+          <t>https://liveatsavoy.com/</t>
+        </is>
+      </c>
+      <c r="Q22" s="3" t="inlineStr">
+        <is>
+          <t>https://www.apartments.com/savoy-sunnyvale-ca/wz9c7ck/</t>
+        </is>
+      </c>
+      <c r="R22" s="2" t="inlineStr">
+        <is>
+          <t>Lawrence</t>
+        </is>
+      </c>
+      <c r="S22" s="2" t="inlineStr">
+        <is>
+          <t>0.6 mi</t>
+        </is>
+      </c>
+      <c r="T22" s="2" t="inlineStr">
+        <is>
+          <t>12 min</t>
+        </is>
+      </c>
+      <c r="U22" s="2" t="inlineStr">
+        <is>
+          <t>A B5 unit for Apr 23 and a B2 unit for Apr 29 were excluded from the eligible interpretation.</t>
+        </is>
+      </c>
+      <c r="V22" s="2" t="inlineStr">
+        <is>
+          <t>2026-03-17</t>
+        </is>
+      </c>
+      <c r="W22" s="2" t="inlineStr">
+        <is>
+          <t>Apartments.com live floor plan page</t>
+        </is>
+      </c>
+      <c r="X22" t="inlineStr">
+        <is>
+          <t>Listed walking time on Apartments.com</t>
+        </is>
+      </c>
+      <c r="Y22" t="inlineStr">
+        <is>
+          <t>In-unit washer/dryer</t>
+        </is>
+      </c>
+      <c r="Z22" t="inlineStr">
+        <is>
+          <t>Apartments.com lists Washer/Dryer under apartment features. The official site does not explicitly mention laundry, but nothing suggests shared-only laundry.</t>
+        </is>
+      </c>
+      <c r="AA22" t="inlineStr">
+        <is>
+          <t>Official site says Savoy is made accessible by Lawrence Station Caltrain and lists the property at 1120 Kifer Road. Apartments.com lists Lawrence at 0.6 mi / 12 min walk and shows washer/dryer in apartment features.</t>
+        </is>
+      </c>
+      <c r="AB22" t="inlineStr">
+        <is>
+          <t>https://liveatsavoy.com/
+https://liveatsavoy.com/amenities/
+https://www.apartments.com/savoy-sunnyvale-ca/wz9c7ck/</t>
+        </is>
+      </c>
+      <c r="AC22" t="inlineStr">
+        <is>
+          <t>2026-03-18</t>
+        </is>
+      </c>
+      <c r="AD22" t="n">
+        <v>0.88</v>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" s="2" t="inlineStr">
+        <is>
+          <t>The Flats at Cityline</t>
+        </is>
+      </c>
+      <c r="B23" s="2" t="inlineStr">
+        <is>
+          <t>Sunnyvale</t>
+        </is>
+      </c>
+      <c r="C23" s="2" t="inlineStr">
+        <is>
+          <t>ELIGIBLE</t>
+        </is>
+      </c>
+      <c r="D23" s="2" t="inlineStr">
+        <is>
+          <t>Now</t>
+        </is>
+      </c>
+      <c r="E23" s="2" t="inlineStr">
+        <is>
+          <t>2026-04-10</t>
+        </is>
+      </c>
+      <c r="F23" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="G23" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="H23" s="2" t="inlineStr">
+        <is>
+          <t>1,123-1,223</t>
+        </is>
+      </c>
+      <c r="I23" s="2" t="inlineStr">
+        <is>
+          <t>$5,187+</t>
+        </is>
+      </c>
+      <c r="J23" s="2" t="inlineStr">
+        <is>
+          <t>Base rent</t>
+        </is>
+      </c>
+      <c r="K23" s="2" t="inlineStr">
+        <is>
+          <t>The Zeppelin and other 2-bed layouts; Redfin showed 10 units available</t>
+        </is>
+      </c>
+      <c r="L23" s="2" t="inlineStr">
+        <is>
+          <t>$1,500 look-and-lease on two-bedroom units</t>
+        </is>
+      </c>
+      <c r="M23" s="2" t="n"/>
+      <c r="N23" s="2" t="n"/>
+      <c r="O23" s="2" t="inlineStr">
+        <is>
+          <t>4.9 (4 reviews)</t>
+        </is>
+      </c>
+      <c r="P23" s="3" t="inlineStr">
+        <is>
+          <t>https://citylineflats.com/</t>
+        </is>
+      </c>
+      <c r="Q23" s="3" t="inlineStr">
+        <is>
+          <t>https://www.apartments.com/the-flats-at-cityline-sunnyvale-ca/0cdemn2/</t>
+        </is>
+      </c>
+      <c r="R23" s="2" t="inlineStr">
+        <is>
+          <t>Sunnyvale</t>
+        </is>
+      </c>
+      <c r="S23" s="2" t="inlineStr">
+        <is>
+          <t>0.2 mi</t>
+        </is>
+      </c>
+      <c r="T23" s="2" t="inlineStr">
+        <is>
+          <t>5 min</t>
+        </is>
+      </c>
+      <c r="U23" s="2" t="inlineStr">
+        <is>
+          <t>This is one of the strongest Sunnyvale transit options, and it is the biggest large-format downtown community in the current set.</t>
+        </is>
+      </c>
+      <c r="V23" s="2" t="inlineStr">
+        <is>
+          <t>2026-03-18</t>
+        </is>
+      </c>
+      <c r="W23" s="2" t="inlineStr">
+        <is>
+          <t>Cityline official site plus Apartments.com exact property page</t>
+        </is>
+      </c>
+      <c r="X23" t="inlineStr">
+        <is>
+          <t>Official Cityline site lists Sunnyvale Station at 0.2 miles / 5 minutes</t>
+        </is>
+      </c>
+      <c r="Y23" t="inlineStr">
+        <is>
+          <t>In-unit washer/dryer</t>
+        </is>
+      </c>
+      <c r="Z23" t="inlineStr">
+        <is>
+          <t>Cityline and Apartments.com both describe an in-home full-size stacked washer and dryer.</t>
+        </is>
+      </c>
+      <c r="AA23" t="inlineStr">
+        <is>
+          <t>Cityline lists Sunnyvale Station at 0.2 miles / 5 minutes and its amenities page lists an in-home full-size washer and dryer. Apartments.com confirms Washer/Dryer in unit features.</t>
+        </is>
+      </c>
+      <c r="AB23" t="inlineStr">
+        <is>
+          <t>https://citylineflats.com/
+https://citylineflats.com/amenities/
+https://www.apartments.com/the-flats-at-cityline-sunnyvale-ca/0cdemn2/
+https://www.redfin.com/neighborhood/119104/CA/Sunnyvale/Heritage-District/2-bedroom-rentals</t>
+        </is>
+      </c>
+      <c r="AC23" t="inlineStr">
+        <is>
+          <t>2026-03-18</t>
+        </is>
+      </c>
+      <c r="AD23" t="n">
+        <v>0.96</v>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" s="2" t="inlineStr">
+        <is>
+          <t>The Martin</t>
+        </is>
+      </c>
+      <c r="B24" s="2" t="inlineStr">
+        <is>
+          <t>Sunnyvale</t>
+        </is>
+      </c>
+      <c r="C24" s="2" t="inlineStr">
+        <is>
+          <t>ELIGIBLE</t>
+        </is>
+      </c>
+      <c r="D24" s="2" t="inlineStr">
+        <is>
+          <t>Now</t>
+        </is>
+      </c>
+      <c r="E24" s="2" t="inlineStr">
+        <is>
+          <t>2026-04-10</t>
+        </is>
+      </c>
+      <c r="F24" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="G24" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="H24" s="2" t="inlineStr">
+        <is>
+          <t>1,000-1,080</t>
+        </is>
+      </c>
+      <c r="I24" s="2" t="inlineStr">
+        <is>
+          <t>$5,153+</t>
+        </is>
+      </c>
+      <c r="J24" s="2" t="inlineStr">
+        <is>
+          <t>Base rent</t>
+        </is>
+      </c>
+      <c r="K24" s="2" t="inlineStr">
+        <is>
+          <t>2-bedroom homes; Redfin showed 27 units available and ApartmentHomeLiving showed a 2-bedroom available Mar 7</t>
+        </is>
+      </c>
+      <c r="L24" s="2" t="n"/>
+      <c r="M24" s="2" t="n"/>
+      <c r="N24" s="2" t="n"/>
+      <c r="O24" s="2" t="inlineStr">
+        <is>
+          <t>not yet verified</t>
+        </is>
+      </c>
+      <c r="P24" s="3" t="inlineStr">
+        <is>
+          <t>https://livethemartin.com/</t>
+        </is>
+      </c>
+      <c r="Q24" s="3" t="inlineStr">
+        <is>
+          <t>https://www.apartmenthomeliving.com/apartment-finder/The-Martin-Sunnyvale-CA-94086-19080754</t>
+        </is>
+      </c>
+      <c r="R24" s="2" t="inlineStr">
+        <is>
+          <t>Sunnyvale</t>
+        </is>
+      </c>
+      <c r="S24" s="2" t="inlineStr">
+        <is>
+          <t>0.4 mi</t>
+        </is>
+      </c>
+      <c r="T24" s="2" t="inlineStr">
+        <is>
+          <t>7 min</t>
+        </is>
+      </c>
+      <c r="U24" s="2" t="inlineStr">
+        <is>
+          <t>Official site confirms the project sits two blocks from Caltrain; third-party listing pages confirm live 2B inventory now.</t>
+        </is>
+      </c>
+      <c r="V24" s="2" t="inlineStr">
+        <is>
+          <t>2026-03-18</t>
+        </is>
+      </c>
+      <c r="W24" s="2" t="inlineStr">
+        <is>
+          <t>Apartments.com exact property page plus Redfin neighborhood rental results</t>
+        </is>
+      </c>
+      <c r="X24" t="inlineStr">
+        <is>
+          <t>Listed walking time/distance from Apartments.com transportation section</t>
+        </is>
+      </c>
+      <c r="Y24" t="inlineStr">
+        <is>
+          <t>In-unit washer/dryer</t>
+        </is>
+      </c>
+      <c r="Z24" t="inlineStr">
+        <is>
+          <t>Apartments.com says washers and dryers are in every home.</t>
+        </is>
+      </c>
+      <c r="AA24" t="inlineStr">
+        <is>
+          <t>Apartments.com shows Sunnyvale Caltrain as a 0.4-mile, 7-minute walk and lists washers and dryers in every home. Redfin and ApartmentHomeLiving both showed current 2-bedroom availability.</t>
+        </is>
+      </c>
+      <c r="AB24" t="inlineStr">
+        <is>
+          <t>https://livethemartin.com/
+https://www.apartments.com/the-martin-sunnyvale-ca/l9flwcd/
+https://www.redfin.com/neighborhood/119104/CA/Sunnyvale/Heritage-District/2-bedroom-rentals
+https://www.apartmenthomeliving.com/apartment-finder/The-Martin-Sunnyvale-CA-94086-19080754</t>
+        </is>
+      </c>
+      <c r="AC24" t="inlineStr">
+        <is>
+          <t>2026-03-18</t>
+        </is>
+      </c>
+      <c r="AD24" t="n">
+        <v>0.9</v>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" s="2" t="inlineStr">
         <is>
           <t>The Meadows Apartments</t>
         </is>
       </c>
-      <c r="B18" s="2" t="inlineStr">
+      <c r="B25" s="2" t="inlineStr">
         <is>
           <t>Sunnyvale</t>
         </is>
       </c>
-      <c r="C18" s="2" t="inlineStr">
+      <c r="C25" s="2" t="inlineStr">
         <is>
           <t>ELIGIBLE</t>
         </is>
       </c>
-      <c r="D18" s="2" t="inlineStr">
+      <c r="D25" s="2" t="inlineStr">
         <is>
           <t>Now</t>
         </is>
       </c>
-      <c r="E18" s="2" t="inlineStr">
+      <c r="E25" s="2" t="inlineStr">
         <is>
           <t>2026-04-10</t>
         </is>
       </c>
-      <c r="F18" s="2" t="inlineStr">
+      <c r="F25" s="2" t="inlineStr">
         <is>
           <t>2</t>
         </is>
       </c>
-      <c r="G18" s="2" t="inlineStr">
+      <c r="G25" s="2" t="inlineStr">
         <is>
           <t>2</t>
         </is>
       </c>
-      <c r="H18" s="2" t="inlineStr">
+      <c r="H25" s="2" t="inlineStr">
         <is>
           <t>915</t>
         </is>
       </c>
-      <c r="I18" s="2" t="inlineStr">
+      <c r="I25" s="2" t="inlineStr">
         <is>
           <t>$4,100-$4,170</t>
         </is>
       </c>
-      <c r="J18" s="2" t="inlineStr">
+      <c r="J25" s="2" t="inlineStr">
         <is>
           <t>Base rent</t>
         </is>
       </c>
-      <c r="K18" s="2" t="inlineStr">
+      <c r="K25" s="2" t="inlineStr">
         <is>
           <t>B2 and B1 floorplans</t>
         </is>
       </c>
-      <c r="L18" s="2" t="inlineStr"/>
-      <c r="M18" s="2" t="inlineStr"/>
-      <c r="N18" s="2" t="inlineStr">
+      <c r="L25" s="2" t="n"/>
+      <c r="M25" s="2" t="n"/>
+      <c r="N25" s="2" t="inlineStr">
         <is>
           <t>Short-term lease available</t>
         </is>
       </c>
-      <c r="O18" s="2" t="inlineStr">
+      <c r="O25" s="2" t="inlineStr">
         <is>
           <t>4.8 (6 reviews)</t>
         </is>
       </c>
-      <c r="P18" s="3" t="inlineStr">
+      <c r="P25" s="3" t="inlineStr">
         <is>
           <t>https://www.the-meadows.com/</t>
         </is>
       </c>
-      <c r="Q18" s="3" t="inlineStr">
+      <c r="Q25" s="3" t="inlineStr">
         <is>
           <t>https://www.apartments.com/the-meadows-apartments-sunnyvale-ca/4fzr7tk/</t>
         </is>
       </c>
-      <c r="R18" s="2" t="inlineStr">
+      <c r="R25" s="2" t="inlineStr">
         <is>
           <t>Sunnyvale</t>
         </is>
       </c>
-      <c r="S18" s="2" t="inlineStr">
+      <c r="S25" s="2" t="inlineStr">
         <is>
           <t>1.5 mi</t>
         </is>
       </c>
-      <c r="T18" s="2" t="inlineStr">
+      <c r="T25" s="2" t="inlineStr">
         <is>
           <t>30 min</t>
         </is>
       </c>
-      <c r="U18" s="2" t="inlineStr">
+      <c r="U25" s="2" t="inlineStr">
         <is>
           <t>Both 2B/2B floorplans were listed as available now; utilities included in listing page include gas, water, heat, trash, sewer, and air conditioning.</t>
         </is>
       </c>
-      <c r="V18" s="2" t="inlineStr">
+      <c r="V25" s="2" t="inlineStr">
         <is>
           <t>2026-03-17</t>
         </is>
       </c>
-      <c r="W18" s="2" t="inlineStr">
+      <c r="W25" s="2" t="inlineStr">
         <is>
           <t>Apartments.com live floor plan page</t>
         </is>
       </c>
-      <c r="X18" t="inlineStr">
+      <c r="X25" t="inlineStr">
         <is>
           <t>Estimated at 20 min/mile from the best available distance; no source exposed an explicit walking route</t>
         </is>
       </c>
-      <c r="Y18" t="inlineStr">
+      <c r="Y25" t="inlineStr">
         <is>
           <t>In-unit washer/dryer</t>
         </is>
       </c>
-      <c r="Z18" t="inlineStr">
+      <c r="Z25" t="inlineStr">
         <is>
           <t>Official amenities page lists Washer &amp; Dryer Included; Apartments.com also shows in-unit washer/dryer.</t>
         </is>
       </c>
-      <c r="AA18" t="inlineStr">
+      <c r="AA25" t="inlineStr">
         <is>
           <t>Official site says the property is a short walk to Caltrain and explicitly lists Washer &amp; Dryer Included. Because no walking route was exposed on listing pages, the walk time is estimated.</t>
         </is>
       </c>
-      <c r="AB18" t="inlineStr">
+      <c r="AB25" t="inlineStr">
         <is>
           <t>https://www.the-meadows.com/apartments/ca/sunnyvale/amenities
 https://www.the-meadows.com/
@@ -3073,156 +4090,157 @@
 https://www.caltrain.com/destinations/sunnyvale</t>
         </is>
       </c>
-      <c r="AC18" t="inlineStr">
+      <c r="AC25" t="inlineStr">
         <is>
           <t>2026-03-18</t>
         </is>
       </c>
-      <c r="AD18" t="n">
+      <c r="AD25" t="n">
         <v>0.76</v>
       </c>
     </row>
-    <row r="19">
-      <c r="A19" s="2" t="inlineStr">
-        <is>
-          <t>Heritage Park</t>
-        </is>
-      </c>
-      <c r="B19" s="2" t="inlineStr">
+    <row r="26">
+      <c r="A26" s="2" t="inlineStr">
+        <is>
+          <t>The Montclaire Apartments</t>
+        </is>
+      </c>
+      <c r="B26" s="2" t="inlineStr">
         <is>
           <t>Sunnyvale</t>
         </is>
       </c>
-      <c r="C19" s="2" t="inlineStr">
+      <c r="C26" s="2" t="inlineStr">
         <is>
           <t>ELIGIBLE</t>
         </is>
       </c>
-      <c r="D19" s="2" t="inlineStr">
+      <c r="D26" s="2" t="inlineStr">
         <is>
           <t>Now</t>
         </is>
       </c>
-      <c r="E19" s="2" t="inlineStr">
+      <c r="E26" s="2" t="inlineStr">
         <is>
           <t>2026-04-10</t>
         </is>
       </c>
-      <c r="F19" s="2" t="inlineStr">
+      <c r="F26" s="2" t="inlineStr">
         <is>
           <t>2</t>
         </is>
       </c>
-      <c r="G19" s="2" t="inlineStr">
+      <c r="G26" s="2" t="inlineStr">
         <is>
           <t>2</t>
         </is>
       </c>
-      <c r="H19" s="2" t="inlineStr">
-        <is>
-          <t>920</t>
-        </is>
-      </c>
-      <c r="I19" s="2" t="inlineStr">
-        <is>
-          <t>$3,280-$4,460</t>
-        </is>
-      </c>
-      <c r="J19" s="2" t="inlineStr">
+      <c r="H26" s="2" t="inlineStr">
+        <is>
+          <t>910</t>
+        </is>
+      </c>
+      <c r="I26" s="2" t="inlineStr">
+        <is>
+          <t>$3,359+</t>
+        </is>
+      </c>
+      <c r="J26" s="2" t="inlineStr">
         <is>
           <t>Base rent</t>
         </is>
       </c>
-      <c r="K19" s="2" t="inlineStr">
-        <is>
-          <t>2x2 / Units 309E now, 1406E now, 1107W now, 409E Apr 8</t>
-        </is>
-      </c>
-      <c r="L19" s="2" t="inlineStr"/>
-      <c r="M19" s="2" t="inlineStr"/>
-      <c r="N19" s="2" t="inlineStr">
-        <is>
-          <t>1-12 months</t>
-        </is>
-      </c>
-      <c r="O19" s="2" t="inlineStr">
-        <is>
-          <t>4.5 (11 reviews)</t>
-        </is>
-      </c>
-      <c r="P19" s="3" t="inlineStr">
-        <is>
-          <t>https://www.liveatheritageparkapts.com/amenities</t>
-        </is>
-      </c>
-      <c r="Q19" s="3" t="inlineStr">
-        <is>
-          <t>https://www.apartments.com/heritage-park-sunnyvale-ca/h2ctem3/</t>
-        </is>
-      </c>
-      <c r="R19" s="2" t="inlineStr">
+      <c r="K26" s="2" t="inlineStr">
+        <is>
+          <t>2 Bed / 2 Bath homes currently marketed in Sunnyvale listings</t>
+        </is>
+      </c>
+      <c r="L26" s="2" t="n"/>
+      <c r="M26" s="2" t="n"/>
+      <c r="N26" s="2" t="inlineStr">
+        <is>
+          <t>Short-term lease available</t>
+        </is>
+      </c>
+      <c r="O26" s="2" t="inlineStr">
+        <is>
+          <t>not yet verified</t>
+        </is>
+      </c>
+      <c r="P26" s="3" t="inlineStr">
+        <is>
+          <t>https://www.essexapartmenthomes.com/apartments/sunnyvale/the-montclaire</t>
+        </is>
+      </c>
+      <c r="Q26" s="3" t="inlineStr">
+        <is>
+          <t>https://www.apartments.com/the-montclaire-sunnyvale-ca/x4m85qp/</t>
+        </is>
+      </c>
+      <c r="R26" s="2" t="inlineStr">
         <is>
           <t>Sunnyvale</t>
         </is>
       </c>
-      <c r="S19" s="2" t="inlineStr">
-        <is>
-          <t>0.7 mi</t>
-        </is>
-      </c>
-      <c r="T19" s="2" t="inlineStr">
-        <is>
-          <t>13 min</t>
-        </is>
-      </c>
-      <c r="U19" s="2" t="inlineStr">
-        <is>
-          <t>A 2x2 unit for Apr 12 was excluded from the eligible interpretation.</t>
-        </is>
-      </c>
-      <c r="V19" s="2" t="inlineStr">
-        <is>
-          <t>2026-03-17</t>
-        </is>
-      </c>
-      <c r="W19" s="2" t="inlineStr">
-        <is>
-          <t>Apartments.com live floor plan page</t>
-        </is>
-      </c>
-      <c r="X19" t="inlineStr">
-        <is>
-          <t>Listed walking time/distance from Apartments.com commuter rail listing</t>
-        </is>
-      </c>
-      <c r="Y19" t="inlineStr">
-        <is>
-          <t>No in-unit washer/dryer</t>
-        </is>
-      </c>
-      <c r="Z19" t="inlineStr">
-        <is>
-          <t>Official amenities list Laundry Facilities as a community amenity, and Apartments.com FAQ says Heritage Park does not provide in-unit laundry and has on-site laundry facilities for shared resident use.</t>
-        </is>
-      </c>
-      <c r="AA19" t="inlineStr">
-        <is>
-          <t>Official site confirms proximity to Sunnyvale Caltrain and lists community laundry facilities. Apartments.com specifies a 13-minute, 0.7-mile walk and states there is no in-unit laundry.</t>
-        </is>
-      </c>
-      <c r="AB19" t="inlineStr">
-        <is>
-          <t>https://www.liveatheritageparkapts.com/amenities
-https://www.apartments.com/heritage-park-sunnyvale-ca/h2ctem3/</t>
-        </is>
-      </c>
-      <c r="AC19" t="inlineStr">
+      <c r="S26" s="2" t="inlineStr">
+        <is>
+          <t>1.1 mi</t>
+        </is>
+      </c>
+      <c r="T26" s="2" t="inlineStr">
+        <is>
+          <t>22 min</t>
+        </is>
+      </c>
+      <c r="U26" s="2" t="inlineStr">
+        <is>
+          <t>Montclaire is now eligible again: current Sunnyvale washer/dryer listings show 2B inventory and the Essex site still markets it as less than one mile from Sunnyvale Caltrain.</t>
+        </is>
+      </c>
+      <c r="V26" s="2" t="inlineStr">
         <is>
           <t>2026-03-18</t>
         </is>
       </c>
-      <c r="AD19" t="n">
-        <v>0.95</v>
+      <c r="W26" s="2" t="inlineStr">
+        <is>
+          <t>Essex official site plus Apartments.com exact property page</t>
+        </is>
+      </c>
+      <c r="X26" t="inlineStr">
+        <is>
+          <t>Estimated from routed walking distance to Sunnyvale Caltrain using a map routing tool because Apartments.com only exposed drive distance to Caltrain</t>
+        </is>
+      </c>
+      <c r="Y26" t="inlineStr">
+        <is>
+          <t>In-unit washer/dryer in select homes</t>
+        </is>
+      </c>
+      <c r="Z26" t="inlineStr">
+        <is>
+          <t>Essex states select homes feature an in-home washer and dryer; Apartments.com repeats the same select-home language.</t>
+        </is>
+      </c>
+      <c r="AA26" t="inlineStr">
+        <is>
+          <t>Essex markets The Montclaire as less than one mile from Sunnyvale Caltrain and says select homes include in-home washer/dryer. Apartments.com shows current 2-bedroom pricing and repeats the select-home laundry language.</t>
+        </is>
+      </c>
+      <c r="AB26" t="inlineStr">
+        <is>
+          <t>https://www.essexapartmenthomes.com/apartments/sunnyvale/the-montclaire
+https://www.apartments.com/the-montclaire-sunnyvale-ca/x4m85qp/
+https://www.apartments.com/downtown-sunnyvale-sunnyvale-ca/washer-dryer/</t>
+        </is>
+      </c>
+      <c r="AC26" t="inlineStr">
+        <is>
+          <t>2026-03-18</t>
+        </is>
+      </c>
+      <c r="AD26" t="n">
+        <v>0.84</v>
       </c>
     </row>
   </sheetData>
@@ -3230,28 +4248,54 @@
   <hyperlinks>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="P2" r:id="rId1"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="Q2" r:id="rId2"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="Q3" r:id="rId3"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="P4" r:id="rId4"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="Q4" r:id="rId5"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="P5" r:id="rId6"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="Q5" r:id="rId7"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="Q6" r:id="rId8"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="Q7" r:id="rId9"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="Q8" r:id="rId10"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="P9" r:id="rId11"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="Q9" r:id="rId12"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="Q10" r:id="rId13"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="Q11" r:id="rId14"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="Q12" r:id="rId15"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="Q13" r:id="rId16"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="Q14" r:id="rId17"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="Q15" r:id="rId18"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="Q16" r:id="rId19"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="Q17" r:id="rId20"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="P18" r:id="rId21"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="Q18" r:id="rId22"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="P19" r:id="rId23"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="Q19" r:id="rId24"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="P3" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="Q3" r:id="rId4"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="P4" r:id="rId5"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="Q4" r:id="rId6"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="P5" r:id="rId7"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="Q5" r:id="rId8"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="P6" r:id="rId9"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="Q6" r:id="rId10"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="P7" r:id="rId11"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="Q7" r:id="rId12"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="P8" r:id="rId13"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="Q8" r:id="rId14"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="P9" r:id="rId15"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="Q9" r:id="rId16"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="P10" r:id="rId17"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="Q10" r:id="rId18"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="P11" r:id="rId19"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="Q11" r:id="rId20"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="P12" r:id="rId21"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="Q12" r:id="rId22"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="P13" r:id="rId23"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="Q13" r:id="rId24"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="P14" r:id="rId25"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="Q14" r:id="rId26"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="P15" r:id="rId27"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="Q15" r:id="rId28"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="P16" r:id="rId29"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="Q16" r:id="rId30"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="P17" r:id="rId31"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="Q17" r:id="rId32"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="P18" r:id="rId33"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="Q18" r:id="rId34"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="P19" r:id="rId35"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="Q19" r:id="rId36"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="P20" r:id="rId37"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="Q20" r:id="rId38"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="P21" r:id="rId39"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="Q21" r:id="rId40"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="P22" r:id="rId41"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="Q22" r:id="rId42"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="P23" r:id="rId43"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="Q23" r:id="rId44"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="P24" r:id="rId45"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="Q24" r:id="rId46"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="P25" r:id="rId47"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="Q25" r:id="rId48"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="P26" r:id="rId49"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="Q26" r:id="rId50"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
